--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
   <si>
     <t/>
   </si>
   <si>
-    <t>10002101</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHIP MRH140</t>
+    <t>20116670</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 65G</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,181 +28,217 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20116686</t>
+  </si>
+  <si>
+    <t>CHTATO LITE C/ONN 68</t>
+  </si>
+  <si>
+    <t>20131037</t>
+  </si>
+  <si>
+    <t>CHTATOLITE ABR.SWD65</t>
+  </si>
+  <si>
+    <t>20132750</t>
+  </si>
+  <si>
+    <t>CHITATO AYAM BWG 65G</t>
+  </si>
+  <si>
+    <t>20046198</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCOLAT 51</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20136951</t>
+  </si>
+  <si>
+    <t>CMORY UHT MATCHA 250</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20140793</t>
+  </si>
+  <si>
+    <t>CIMORY UHT MTCHA 225</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20116684</t>
+  </si>
+  <si>
+    <t>CHTATO LITE SLMON 68</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
+    <t>20099571</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20140795</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOCO 225</t>
+  </si>
+  <si>
+    <t>20140794</t>
+  </si>
+  <si>
+    <t>CIMORY UHT MARIE 225</t>
+  </si>
+  <si>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20016864</t>
+  </si>
+  <si>
+    <t>CSSN BW RFRSH 2/3X45</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20023845</t>
-  </si>
-  <si>
-    <t>PRINGLES CHEESY 102G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20023846</t>
-  </si>
-  <si>
-    <t>PRNGLES ORIGNAL 102G</t>
-  </si>
-  <si>
-    <t>20044093</t>
-  </si>
-  <si>
-    <t>PRNGLES S.CRM&amp;O 102G</t>
-  </si>
-  <si>
-    <t>20119019</t>
-  </si>
-  <si>
-    <t>HAPPYTOS HOT CHL 140</t>
-  </si>
-  <si>
-    <t>10000213</t>
-  </si>
-  <si>
-    <t>GLICO POCKY CHO 47GR</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10036916</t>
-  </si>
-  <si>
-    <t>GLICO POCKY.STRAW 45</t>
-  </si>
-  <si>
-    <t>20057865</t>
-  </si>
-  <si>
-    <t>GLCO POCKY DOU.CHO47</t>
-  </si>
-  <si>
-    <t>20062839</t>
-  </si>
-  <si>
-    <t>GLCO POCKY MTCHA 33G</t>
-  </si>
-  <si>
-    <t>20086168</t>
-  </si>
-  <si>
-    <t>GLCO POCKY COOK&amp;CR40</t>
-  </si>
-  <si>
-    <t>20138740</t>
-  </si>
-  <si>
-    <t>POCKY MILK CHOCO 39G</t>
-  </si>
-  <si>
-    <t>20138741</t>
-  </si>
-  <si>
-    <t>GLICO POCKY MILK 39G</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
-  </si>
-  <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
-  </si>
-  <si>
-    <t>20113083</t>
-  </si>
-  <si>
-    <t>TESSA FC.TISU 2X200S</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20131788</t>
-  </si>
-  <si>
-    <t>MAMA LMN JR.NPS 950</t>
-  </si>
-  <si>
-    <t>20040217</t>
-  </si>
-  <si>
-    <t>LFBUOY BW C.FRSH 400</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20041399</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 400</t>
-  </si>
-  <si>
-    <t>20011007</t>
-  </si>
-  <si>
-    <t>LFBUOY BW M.CARE 400</t>
-  </si>
-  <si>
-    <t>20011008</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 400</t>
+    <t>20087203</t>
+  </si>
+  <si>
+    <t>CSSN BW FRS&amp;N 2/3X45</t>
+  </si>
+  <si>
+    <t>20038758</t>
+  </si>
+  <si>
+    <t>PANTENE CND HFC 160</t>
+  </si>
+  <si>
+    <t>PT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20038763</t>
+  </si>
+  <si>
+    <t>PNTENE SHP ANT/D 160</t>
+  </si>
+  <si>
+    <t>20038766</t>
+  </si>
+  <si>
+    <t>PANTENE SHP HFC 160</t>
+  </si>
+  <si>
+    <t>20038770</t>
+  </si>
+  <si>
+    <t>PNTENE SHP SM.CR 160</t>
+  </si>
+  <si>
+    <t>20038986</t>
+  </si>
+  <si>
+    <t>PNTENE SHP LG BLK160</t>
+  </si>
+  <si>
+    <t>20039727</t>
+  </si>
+  <si>
+    <t>SHINZU'I MATSU 380ML</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20039728</t>
+  </si>
+  <si>
+    <t>SHINZU'I KIREI 380ML</t>
+  </si>
+  <si>
+    <t>20130653</t>
+  </si>
+  <si>
+    <t>SHINZU'I SKURA 380ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
+  </si>
+  <si>
+    <t>20037446</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ ROSE 700</t>
+  </si>
+  <si>
+    <t>20138867</t>
+  </si>
+  <si>
+    <t>RNSO JAP PEACH 700G</t>
+  </si>
+  <si>
+    <t>PT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20141203</t>
+  </si>
+  <si>
+    <t>RINSO RYL GOLD 700G</t>
+  </si>
+  <si>
+    <t>20141369</t>
+  </si>
+  <si>
+    <t>RINSO P.BRZE BTL 650</t>
+  </si>
+  <si>
+    <t>20141373</t>
+  </si>
+  <si>
+    <t>RINSO PW.CLN BTL 650</t>
   </si>
 </sst>
 </file>
@@ -595,14 +631,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -662,16 +698,16 @@
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
@@ -682,16 +718,16 @@
         <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -702,35 +738,35 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -739,18 +775,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -759,207 +795,207 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>43</v>
@@ -967,182 +1003,262 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>57</v>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="82">
   <si>
     <t/>
   </si>
   <si>
-    <t>20116670</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 65G</t>
+    <t>20055311</t>
+  </si>
+  <si>
+    <t>NABATI RCHSE WFR 110</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,31 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20116686</t>
-  </si>
-  <si>
-    <t>CHTATO LITE C/ONN 68</t>
-  </si>
-  <si>
-    <t>20131037</t>
-  </si>
-  <si>
-    <t>CHTATOLITE ABR.SWD65</t>
-  </si>
-  <si>
-    <t>20132750</t>
-  </si>
-  <si>
-    <t>CHITATO AYAM BWG 65G</t>
-  </si>
-  <si>
-    <t>20046198</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCOLAT 51</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20138462</t>
+  </si>
+  <si>
+    <t>NABATI WFR STRAW 122</t>
   </si>
   <si>
     <t>2</t>
@@ -61,184 +43,220 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20136951</t>
-  </si>
-  <si>
-    <t>CMORY UHT MATCHA 250</t>
+    <t>20055312</t>
+  </si>
+  <si>
+    <t>NBATI RCHCO WFR C110</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20140793</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MTCHA 225</t>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA STERIL189</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20116684</t>
-  </si>
-  <si>
-    <t>CHTATO LITE SLMON 68</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>20099571</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20140795</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 225</t>
-  </si>
-  <si>
-    <t>20140794</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MARIE 225</t>
-  </si>
-  <si>
-    <t>20131625</t>
-  </si>
-  <si>
-    <t>LARISST FCL.TIS 250S</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20016864</t>
-  </si>
-  <si>
-    <t>CSSN BW RFRSH 2/3X45</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20087203</t>
-  </si>
-  <si>
-    <t>CSSN BW FRS&amp;N 2/3X45</t>
-  </si>
-  <si>
-    <t>20038758</t>
-  </si>
-  <si>
-    <t>PANTENE CND HFC 160</t>
-  </si>
-  <si>
-    <t>PT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20038763</t>
-  </si>
-  <si>
-    <t>PNTENE SHP ANT/D 160</t>
-  </si>
-  <si>
-    <t>20038766</t>
-  </si>
-  <si>
-    <t>PANTENE SHP HFC 160</t>
-  </si>
-  <si>
-    <t>20038770</t>
-  </si>
-  <si>
-    <t>PNTENE SHP SM.CR 160</t>
-  </si>
-  <si>
-    <t>20038986</t>
-  </si>
-  <si>
-    <t>PNTENE SHP LG BLK160</t>
-  </si>
-  <si>
-    <t>20039727</t>
-  </si>
-  <si>
-    <t>SHINZU'I MATSU 380ML</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20039728</t>
-  </si>
-  <si>
-    <t>SHINZU'I KIREI 380ML</t>
-  </si>
-  <si>
-    <t>20130653</t>
-  </si>
-  <si>
-    <t>SHINZU'I SKURA 380ML</t>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20125555</t>
+  </si>
+  <si>
+    <t>SEDAP MI KRN CH/BL86</t>
+  </si>
+  <si>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
+  </si>
+  <si>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM BWG70</t>
+  </si>
+  <si>
+    <t>10023791</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KR.AYAM72</t>
+  </si>
+  <si>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
+  </si>
+  <si>
+    <t>20025418</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KARI SP75</t>
+  </si>
+  <si>
+    <t>20049556</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM KR 88</t>
+  </si>
+  <si>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>20114755</t>
+  </si>
+  <si>
+    <t>SDP MIE SPC.LAKSA 83</t>
+  </si>
+  <si>
+    <t>20123024</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO.MDR82</t>
+  </si>
+  <si>
+    <t>20131690</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM JRT77</t>
+  </si>
+  <si>
+    <t>20136385</t>
+  </si>
+  <si>
+    <t>SEDAAP GRG CHF.DVN93</t>
+  </si>
+  <si>
+    <t>20040217</t>
+  </si>
+  <si>
+    <t>LFBUOY BW C.FRSH 400</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20011007</t>
+  </si>
+  <si>
+    <t>LFBUOY BW M.CARE 400</t>
+  </si>
+  <si>
+    <t>20011008</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 400</t>
+  </si>
+  <si>
+    <t>20041399</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 400</t>
+  </si>
+  <si>
+    <t>20041483</t>
+  </si>
+  <si>
+    <t>SO/KLN SOFT P/RS1.44</t>
+  </si>
+  <si>
+    <t>20073805</t>
+  </si>
+  <si>
+    <t>SOKLN RED/MG&amp;B1.44KG</t>
+  </si>
+  <si>
+    <t>20099414</t>
+  </si>
+  <si>
+    <t>SOKLIN SOFT PRPL1.44</t>
+  </si>
+  <si>
+    <t>20140804</t>
+  </si>
+  <si>
+    <t>SO KLN EDP BLNC 1.44</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20140806</t>
+  </si>
+  <si>
+    <t>SO KLN EDP D.LS 144</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
     <t>20112491</t>
   </si>
   <si>
     <t>SNLIGHT LIME PCH 910</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
     <t>20139728</t>
   </si>
   <si>
     <t>SNLGHT BIO BLBR 870G</t>
   </si>
   <si>
-    <t>20037446</t>
-  </si>
-  <si>
-    <t>RNSO+ML LIQ ROSE 700</t>
-  </si>
-  <si>
-    <t>20138867</t>
-  </si>
-  <si>
-    <t>RNSO JAP PEACH 700G</t>
-  </si>
-  <si>
-    <t>PT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20141203</t>
-  </si>
-  <si>
-    <t>RINSO RYL GOLD 700G</t>
-  </si>
-  <si>
-    <t>20141369</t>
-  </si>
-  <si>
-    <t>RINSO P.BRZE BTL 650</t>
-  </si>
-  <si>
-    <t>20141373</t>
-  </si>
-  <si>
-    <t>RINSO PW.CLN BTL 650</t>
+    <t>20040608</t>
+  </si>
+  <si>
+    <t>ZINC SHP HFT GNSG170</t>
+  </si>
+  <si>
+    <t>20040609</t>
+  </si>
+  <si>
+    <t>ZINC RE-FRSH COOL170</t>
+  </si>
+  <si>
+    <t>20109265</t>
+  </si>
+  <si>
+    <t>ZINC SHP LMN MINT170</t>
+  </si>
+  <si>
+    <t>20136708</t>
+  </si>
+  <si>
+    <t>ZINC SHP COOL.BS 170</t>
   </si>
 </sst>
 </file>
@@ -631,14 +649,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -695,18 +713,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -715,7 +733,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -723,10 +741,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -735,70 +753,70 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -812,13 +830,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -832,13 +850,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -852,13 +870,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -872,13 +890,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -892,13 +910,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -912,353 +930,453 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>62</v>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="54">
   <si>
     <t/>
   </si>
   <si>
-    <t>20055311</t>
-  </si>
-  <si>
-    <t>NABATI RCHSE WFR 110</t>
+    <t>10025301</t>
+  </si>
+  <si>
+    <t>QUAKER OAT MERAH 800</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,235 +28,151 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20138462</t>
-  </si>
-  <si>
-    <t>NABATI WFR STRAW 122</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20055312</t>
-  </si>
-  <si>
-    <t>NBATI RCHCO WFR C110</t>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20125555</t>
-  </si>
-  <si>
-    <t>SEDAP MI KRN CH/BL86</t>
-  </si>
-  <si>
-    <t>10023789</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GORENG 91</t>
-  </si>
-  <si>
-    <t>10023790</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM BWG70</t>
-  </si>
-  <si>
-    <t>10023791</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KR.AYAM72</t>
-  </si>
-  <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
-  </si>
-  <si>
-    <t>20025418</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KARI SP75</t>
-  </si>
-  <si>
-    <t>20049556</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM KR 88</t>
-  </si>
-  <si>
-    <t>20096781</t>
-  </si>
-  <si>
-    <t>SEDAAP MI KR.SPCY 87</t>
-  </si>
-  <si>
-    <t>20114755</t>
-  </si>
-  <si>
-    <t>SDP MIE SPC.LAKSA 83</t>
-  </si>
-  <si>
-    <t>20123024</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO.MDR82</t>
-  </si>
-  <si>
-    <t>20131690</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM JRT77</t>
-  </si>
-  <si>
-    <t>20136385</t>
-  </si>
-  <si>
-    <t>SEDAAP GRG CHF.DVN93</t>
-  </si>
-  <si>
-    <t>20040217</t>
-  </si>
-  <si>
-    <t>LFBUOY BW C.FRSH 400</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20011007</t>
-  </si>
-  <si>
-    <t>LFBUOY BW M.CARE 400</t>
-  </si>
-  <si>
-    <t>20011008</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 400</t>
-  </si>
-  <si>
-    <t>20041399</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 400</t>
-  </si>
-  <si>
-    <t>20041483</t>
-  </si>
-  <si>
-    <t>SO/KLN SOFT P/RS1.44</t>
-  </si>
-  <si>
-    <t>20073805</t>
-  </si>
-  <si>
-    <t>SOKLN RED/MG&amp;B1.44KG</t>
-  </si>
-  <si>
-    <t>20099414</t>
-  </si>
-  <si>
-    <t>SOKLIN SOFT PRPL1.44</t>
-  </si>
-  <si>
-    <t>20140804</t>
-  </si>
-  <si>
-    <t>SO KLN EDP BLNC 1.44</t>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
+  </si>
+  <si>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
+  </si>
+  <si>
+    <t>20136102</t>
+  </si>
+  <si>
+    <t>IDM SOES STROBERI80G</t>
+  </si>
+  <si>
+    <t>20139684</t>
+  </si>
+  <si>
+    <t>FIESTA BAKSO MN.LAVA</t>
+  </si>
+  <si>
+    <t>RT,(E-7H)</t>
+  </si>
+  <si>
+    <t>20139683</t>
+  </si>
+  <si>
+    <t>FIESTA RTG H.LAVA 60</t>
+  </si>
+  <si>
+    <t>20138476</t>
+  </si>
+  <si>
+    <t>FIESTA S.RTG H.BBQ60</t>
+  </si>
+  <si>
+    <t>20138976</t>
+  </si>
+  <si>
+    <t>FIESTA BAKSO CH.LV55</t>
+  </si>
+  <si>
+    <t>20139682</t>
+  </si>
+  <si>
+    <t>FIESTA RTG C.LAVA 60</t>
+  </si>
+  <si>
+    <t>20140367</t>
+  </si>
+  <si>
+    <t>FIESTA SS MENTAI 60G</t>
+  </si>
+  <si>
+    <t>10014168</t>
+  </si>
+  <si>
+    <t>NICE BUY1FREE1 2X200</t>
   </si>
   <si>
     <t>RT</t>
   </si>
   <si>
-    <t>20140806</t>
-  </si>
-  <si>
-    <t>SO KLN EDP D.LS 144</t>
-  </si>
-  <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20112491</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 910</t>
-  </si>
-  <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
-  </si>
-  <si>
-    <t>20040608</t>
-  </si>
-  <si>
-    <t>ZINC SHP HFT GNSG170</t>
-  </si>
-  <si>
-    <t>20040609</t>
-  </si>
-  <si>
-    <t>ZINC RE-FRSH COOL170</t>
-  </si>
-  <si>
-    <t>20109265</t>
-  </si>
-  <si>
-    <t>ZINC SHP LMN MINT170</t>
-  </si>
-  <si>
-    <t>20136708</t>
-  </si>
-  <si>
-    <t>ZINC SHP COOL.BS 170</t>
+    <t>20101378</t>
+  </si>
+  <si>
+    <t>KODOMO B.WIPE PNK 50</t>
+  </si>
+  <si>
+    <t>20121413</t>
+  </si>
+  <si>
+    <t>KDMO B.WP ALOE 2X50S</t>
+  </si>
+  <si>
+    <t>20138518</t>
+  </si>
+  <si>
+    <t>KILAU NIPIS 630ML</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20060393</t>
+  </si>
+  <si>
+    <t>NUVO CAIR CLSC 400</t>
+  </si>
+  <si>
+    <t>20063269</t>
+  </si>
+  <si>
+    <t>NUVO CAIR NATURE 400</t>
+  </si>
+  <si>
+    <t>20060392</t>
+  </si>
+  <si>
+    <t>NUVO CAIR CARING 400</t>
+  </si>
+  <si>
+    <t>20114112</t>
+  </si>
+  <si>
+    <t>NUVO FRS.PRO LMN 400</t>
+  </si>
+  <si>
+    <t>20138658</t>
+  </si>
+  <si>
+    <t>NUVO BW HYGIENIC 400</t>
   </si>
 </sst>
 </file>
@@ -649,14 +565,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -716,15 +632,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -733,7 +649,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -741,10 +657,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -753,38 +669,38 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -793,18 +709,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -813,39 +729,39 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
@@ -853,19 +769,19 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
@@ -873,19 +789,19 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
@@ -893,19 +809,19 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
@@ -913,19 +829,19 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
@@ -933,30 +849,30 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,13 +886,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -990,13 +906,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1010,73 +926,73 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1090,13 +1006,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1110,273 +1026,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="55">
   <si>
     <t/>
   </si>
   <si>
-    <t>10025301</t>
-  </si>
-  <si>
-    <t>QUAKER OAT MERAH 800</t>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,151 +28,154 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT FULL CRM 946</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
+    <t>20014071</t>
+  </si>
+  <si>
+    <t>FF UHT CHOCO 946ML</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KURMA SUSU KR189</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
-  </si>
-  <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
-  </si>
-  <si>
-    <t>20136102</t>
-  </si>
-  <si>
-    <t>IDM SOES STROBERI80G</t>
-  </si>
-  <si>
-    <t>20139684</t>
-  </si>
-  <si>
-    <t>FIESTA BAKSO MN.LAVA</t>
-  </si>
-  <si>
-    <t>RT,(E-7H)</t>
-  </si>
-  <si>
-    <t>20139683</t>
-  </si>
-  <si>
-    <t>FIESTA RTG H.LAVA 60</t>
-  </si>
-  <si>
-    <t>20138476</t>
-  </si>
-  <si>
-    <t>FIESTA S.RTG H.BBQ60</t>
-  </si>
-  <si>
-    <t>20138976</t>
-  </si>
-  <si>
-    <t>FIESTA BAKSO CH.LV55</t>
-  </si>
-  <si>
-    <t>20139682</t>
-  </si>
-  <si>
-    <t>FIESTA RTG C.LAVA 60</t>
-  </si>
-  <si>
-    <t>20140367</t>
-  </si>
-  <si>
-    <t>FIESTA SS MENTAI 60G</t>
-  </si>
-  <si>
-    <t>10014168</t>
-  </si>
-  <si>
-    <t>NICE BUY1FREE1 2X200</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20101378</t>
-  </si>
-  <si>
-    <t>KODOMO B.WIPE PNK 50</t>
-  </si>
-  <si>
-    <t>20121413</t>
-  </si>
-  <si>
-    <t>KDMO B.WP ALOE 2X50S</t>
-  </si>
-  <si>
-    <t>20138518</t>
-  </si>
-  <si>
-    <t>KILAU NIPIS 630ML</t>
+    <t>20122571</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PG 115G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20134572</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPRK 115</t>
+  </si>
+  <si>
+    <t>20130152</t>
+  </si>
+  <si>
+    <t>LEMONILO BROWNIES 33</t>
+  </si>
+  <si>
+    <t>20132494</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS KJU33</t>
+  </si>
+  <si>
+    <t>20137230</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS STR33</t>
+  </si>
+  <si>
+    <t>20138902</t>
+  </si>
+  <si>
+    <t>SNSLK SHP S.SMTH 320</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20138903</t>
+  </si>
+  <si>
+    <t>SNSLK SHP G.BLCK 320</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20137792</t>
+  </si>
+  <si>
+    <t>MAMA LIME GREEN 690</t>
   </si>
   <si>
     <t>RT,(E-1.5B)</t>
   </si>
   <si>
-    <t>20060393</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CLSC 400</t>
-  </si>
-  <si>
-    <t>20063269</t>
-  </si>
-  <si>
-    <t>NUVO CAIR NATURE 400</t>
-  </si>
-  <si>
-    <t>20060392</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CARING 400</t>
-  </si>
-  <si>
-    <t>20114112</t>
-  </si>
-  <si>
-    <t>NUVO FRS.PRO LMN 400</t>
-  </si>
-  <si>
-    <t>20138658</t>
-  </si>
-  <si>
-    <t>NUVO BW HYGIENIC 400</t>
+    <t>10004067</t>
+  </si>
+  <si>
+    <t>MAMA/L PCH LEMON 690</t>
+  </si>
+  <si>
+    <t>10004068</t>
+  </si>
+  <si>
+    <t>MAMA LIME POUCH 690</t>
+  </si>
+  <si>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 690</t>
+  </si>
+  <si>
+    <t>20052031</t>
+  </si>
+  <si>
+    <t>MAMA LIME GRN TEA690</t>
+  </si>
+  <si>
+    <t>20099424</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 690</t>
+  </si>
+  <si>
+    <t>20134303</t>
+  </si>
+  <si>
+    <t>MAMA/L REF YUZU 690</t>
   </si>
 </sst>
 </file>
@@ -565,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -632,27 +635,27 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -672,15 +675,15 @@
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -692,35 +695,35 @@
         <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -732,15 +735,15 @@
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -749,7 +752,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>23</v>
@@ -757,10 +760,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -769,18 +772,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -789,18 +792,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -809,230 +812,210 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="64">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
+    <t>20138236</t>
+  </si>
+  <si>
+    <t>CHEETOS JGG BKR 120G</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,154 +28,181 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138241</t>
+  </si>
+  <si>
+    <t>CHEETOS KEJU 120G</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20014071</t>
-  </si>
-  <si>
-    <t>FF UHT CHOCO 946ML</t>
-  </si>
-  <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20114494</t>
+  </si>
+  <si>
+    <t>NSCAFE CRML MCTO 220</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20122571</t>
-  </si>
-  <si>
-    <t>PIATTOS SAPI PG 115G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20134572</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPRK 115</t>
-  </si>
-  <si>
-    <t>20130152</t>
-  </si>
-  <si>
-    <t>LEMONILO BROWNIES 33</t>
-  </si>
-  <si>
-    <t>20132494</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS KJU33</t>
-  </si>
-  <si>
-    <t>20137230</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS STR33</t>
-  </si>
-  <si>
-    <t>20138902</t>
-  </si>
-  <si>
-    <t>SNSLK SHP S.SMTH 320</t>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE ICE BLACK 220</t>
+  </si>
+  <si>
+    <t>20138057</t>
+  </si>
+  <si>
+    <t>NSCAFE GULA AREN 220</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
+  </si>
+  <si>
+    <t>20107729</t>
+  </si>
+  <si>
+    <t>TOP COFF GL AREN 9'S</t>
+  </si>
+  <si>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20041562</t>
+  </si>
+  <si>
+    <t>TOP COFFEE SUSU 10'S</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20095226</t>
+  </si>
+  <si>
+    <t>TOP COFF CAPPCNO 6'S</t>
+  </si>
+  <si>
+    <t>20130895</t>
+  </si>
+  <si>
+    <t>T/C KPI SS GL.ARN 9S</t>
+  </si>
+  <si>
+    <t>20134965</t>
+  </si>
+  <si>
+    <t>TOP/COFF MKACHNO 198</t>
+  </si>
+  <si>
+    <t>20038758</t>
+  </si>
+  <si>
+    <t>PANTENE CND HFC 160</t>
+  </si>
+  <si>
+    <t>PT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20038763</t>
+  </si>
+  <si>
+    <t>PNTENE SHP ANT/D 160</t>
+  </si>
+  <si>
+    <t>20038766</t>
+  </si>
+  <si>
+    <t>PANTENE SHP HFC 160</t>
+  </si>
+  <si>
+    <t>20038770</t>
+  </si>
+  <si>
+    <t>PNTENE SHP SM.CR 160</t>
+  </si>
+  <si>
+    <t>20038986</t>
+  </si>
+  <si>
+    <t>PNTENE SHP LG BLK160</t>
+  </si>
+  <si>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20138903</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 320</t>
-  </si>
-  <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20137792</t>
-  </si>
-  <si>
-    <t>MAMA LIME GREEN 690</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>MAMA/L PCH LEMON 690</t>
-  </si>
-  <si>
-    <t>10004068</t>
-  </si>
-  <si>
-    <t>MAMA LIME POUCH 690</t>
-  </si>
-  <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 690</t>
-  </si>
-  <si>
-    <t>20052031</t>
-  </si>
-  <si>
-    <t>MAMA LIME GRN TEA690</t>
-  </si>
-  <si>
-    <t>20099424</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 690</t>
-  </si>
-  <si>
-    <t>20134303</t>
-  </si>
-  <si>
-    <t>MAMA/L REF YUZU 690</t>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
+  </si>
+  <si>
+    <t>20128974</t>
+  </si>
+  <si>
+    <t>MONTISS FC TISUE200S</t>
+  </si>
+  <si>
+    <t>RT</t>
   </si>
 </sst>
 </file>
@@ -568,14 +595,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -632,39 +659,39 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -672,350 +699,430 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>42</v>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="73">
   <si>
     <t/>
   </si>
   <si>
-    <t>20138236</t>
-  </si>
-  <si>
-    <t>CHEETOS JGG BKR 120G</t>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,181 +28,208 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20138241</t>
-  </si>
-  <si>
-    <t>CHEETOS KEJU 120G</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NESCAFE LATTE 220ML</t>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20114494</t>
-  </si>
-  <si>
-    <t>NSCAFE CRML MCTO 220</t>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NESCAFE CPUCCINO 220</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE ICE BLACK 220</t>
-  </si>
-  <si>
-    <t>20138057</t>
-  </si>
-  <si>
-    <t>NSCAFE GULA AREN 220</t>
-  </si>
-  <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
-  </si>
-  <si>
-    <t>20120855</t>
-  </si>
-  <si>
-    <t>INDOMILK SWIS CHO535</t>
-  </si>
-  <si>
-    <t>20107729</t>
-  </si>
-  <si>
-    <t>TOP COFF GL AREN 9'S</t>
-  </si>
-  <si>
-    <t>RT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20041562</t>
-  </si>
-  <si>
-    <t>TOP COFFEE SUSU 10'S</t>
+    <t>10003485</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO ALMOND 52G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10036987</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO CASHEW 52G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI CARB80</t>
+  </si>
+  <si>
+    <t>20135313</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI BOLOG76</t>
+  </si>
+  <si>
+    <t>20137860</t>
+  </si>
+  <si>
+    <t>WOW AGLI OLIO 75G</t>
+  </si>
+  <si>
+    <t>20045609</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE BSO CUP77</t>
+  </si>
+  <si>
+    <t>20045610</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO CUP81</t>
+  </si>
+  <si>
+    <t>20045611</t>
+  </si>
+  <si>
+    <t>SEDAAP MI GRNG CUP85</t>
+  </si>
+  <si>
+    <t>20052391</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE K/S CUP81</t>
+  </si>
+  <si>
+    <t>20099297</t>
+  </si>
+  <si>
+    <t>SDAAP MIE SP.CHKN 81</t>
+  </si>
+  <si>
+    <t>20113844</t>
+  </si>
+  <si>
+    <t>SEDAAP MI AYM JRT 75</t>
+  </si>
+  <si>
+    <t>20122255</t>
+  </si>
+  <si>
+    <t>SDP MI BASO BLDK 77G</t>
+  </si>
+  <si>
+    <t>20135720</t>
+  </si>
+  <si>
+    <t>SDP MI KARI MRCON79G</t>
+  </si>
+  <si>
+    <t>20140678</t>
+  </si>
+  <si>
+    <t>SEDAAP SPC LAKSA CUP</t>
+  </si>
+  <si>
+    <t>10011850</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP MNT DNGN 160</t>
+  </si>
+  <si>
+    <t>PT,(E-5B)</t>
+  </si>
+  <si>
+    <t>10011851</t>
+  </si>
+  <si>
+    <t>H&amp;S A/D SMTH&amp;SLK 160</t>
+  </si>
+  <si>
+    <t>20049799</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP LMON FRS 160</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20118299</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP SPRM A.HF135</t>
+  </si>
+  <si>
+    <t>20039727</t>
+  </si>
+  <si>
+    <t>SHINZU'I MATSU 380ML</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20095226</t>
-  </si>
-  <si>
-    <t>TOP COFF CAPPCNO 6'S</t>
-  </si>
-  <si>
-    <t>20130895</t>
-  </si>
-  <si>
-    <t>T/C KPI SS GL.ARN 9S</t>
-  </si>
-  <si>
-    <t>20134965</t>
-  </si>
-  <si>
-    <t>TOP/COFF MKACHNO 198</t>
-  </si>
-  <si>
-    <t>20038758</t>
-  </si>
-  <si>
-    <t>PANTENE CND HFC 160</t>
-  </si>
-  <si>
-    <t>PT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20038763</t>
-  </si>
-  <si>
-    <t>PNTENE SHP ANT/D 160</t>
-  </si>
-  <si>
-    <t>20038766</t>
-  </si>
-  <si>
-    <t>PANTENE SHP HFC 160</t>
-  </si>
-  <si>
-    <t>20038770</t>
-  </si>
-  <si>
-    <t>PNTENE SHP SM.CR 160</t>
-  </si>
-  <si>
-    <t>20038986</t>
-  </si>
-  <si>
-    <t>PNTENE SHP LG BLK160</t>
-  </si>
-  <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20112491</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 910</t>
+    <t>20039728</t>
+  </si>
+  <si>
+    <t>SHINZU'I KIREI 380ML</t>
+  </si>
+  <si>
+    <t>20130653</t>
+  </si>
+  <si>
+    <t>SHINZU'I SKURA 380ML</t>
+  </si>
+  <si>
+    <t>20133798</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ EN.RS700</t>
+  </si>
+  <si>
+    <t>20135245</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ FRNCH700</t>
+  </si>
+  <si>
+    <t>20139729</t>
+  </si>
+  <si>
+    <t>SOKLN GR.TEA&amp;JSM 700</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
   </si>
   <si>
     <t>PT</t>
-  </si>
-  <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
-  </si>
-  <si>
-    <t>20128974</t>
-  </si>
-  <si>
-    <t>MONTISS FC TISUE200S</t>
-  </si>
-  <si>
-    <t>RT</t>
   </si>
 </sst>
 </file>
@@ -595,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -659,18 +686,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -679,18 +706,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -699,18 +726,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -719,18 +746,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -739,150 +766,150 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -896,13 +923,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -916,13 +943,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -936,13 +963,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -956,53 +983,53 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1016,13 +1043,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1036,33 +1063,33 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1076,10 +1103,10 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>58</v>
@@ -1096,10 +1123,10 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>58</v>
@@ -1116,13 +1143,93 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>63</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="70">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,208 +28,199 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
+  </si>
+  <si>
+    <t>10025006</t>
+  </si>
+  <si>
+    <t>NESTLE KOKO.COMBO 30</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20046903</t>
+  </si>
+  <si>
+    <t>NESTLE HONY STAR 30G</t>
+  </si>
+  <si>
+    <t>20111959</t>
+  </si>
+  <si>
+    <t>KOKO KRNCH DB.CHO 30</t>
+  </si>
+  <si>
+    <t>20032723</t>
+  </si>
+  <si>
+    <t>MILO CEREAL COKLT 30</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10004490</t>
+  </si>
+  <si>
+    <t>HELLO PANDA STRW 42G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10038704</t>
+  </si>
+  <si>
+    <t>MEIJI H/PANDA CHOC42</t>
+  </si>
+  <si>
+    <t>20134559</t>
+  </si>
+  <si>
+    <t>HLO PANDA DB.CHO 42G</t>
+  </si>
+  <si>
+    <t>20107748</t>
+  </si>
+  <si>
+    <t>MILKU SUSU CKLT 200</t>
+  </si>
+  <si>
+    <t>20107749</t>
+  </si>
+  <si>
+    <t>MILKU SUSU STRO 200</t>
+  </si>
+  <si>
+    <t>20134047</t>
+  </si>
+  <si>
+    <t>MILKU SUSU ORGNAL200</t>
+  </si>
+  <si>
+    <t>20141102</t>
+  </si>
+  <si>
+    <t>MILKU UHT MARIE 200</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
+    <t>20034685</t>
+  </si>
+  <si>
+    <t>OISHI PILLOW CHO 100</t>
+  </si>
+  <si>
+    <t>20034686</t>
+  </si>
+  <si>
+    <t>OISHI PILLOW UBI 100</t>
+  </si>
+  <si>
+    <t>20045784</t>
+  </si>
+  <si>
+    <t>OISHI SPNG/C CHO 100</t>
+  </si>
+  <si>
+    <t>20047335</t>
+  </si>
+  <si>
+    <t>OISHI SPNG STRW 100G</t>
+  </si>
+  <si>
+    <t>20136289</t>
+  </si>
+  <si>
+    <t>OISHI SPONGE UBI 100</t>
+  </si>
+  <si>
+    <t>20141746</t>
+  </si>
+  <si>
+    <t>OISHI PLLOW STRW 100</t>
+  </si>
+  <si>
+    <t>20073377</t>
+  </si>
+  <si>
+    <t>GRNIER MC.CLN PNK125</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20113219</t>
+  </si>
+  <si>
+    <t>GNR MCL/WTR VITC 125</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10003485</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO ALMOND 52G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI CARB80</t>
-  </si>
-  <si>
-    <t>20135313</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI BOLOG76</t>
-  </si>
-  <si>
-    <t>20137860</t>
-  </si>
-  <si>
-    <t>WOW AGLI OLIO 75G</t>
-  </si>
-  <si>
-    <t>20045609</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE BSO CUP77</t>
-  </si>
-  <si>
-    <t>20045610</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO CUP81</t>
-  </si>
-  <si>
-    <t>20045611</t>
-  </si>
-  <si>
-    <t>SEDAAP MI GRNG CUP85</t>
-  </si>
-  <si>
-    <t>20052391</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE K/S CUP81</t>
-  </si>
-  <si>
-    <t>20099297</t>
-  </si>
-  <si>
-    <t>SDAAP MIE SP.CHKN 81</t>
-  </si>
-  <si>
-    <t>20113844</t>
-  </si>
-  <si>
-    <t>SEDAAP MI AYM JRT 75</t>
-  </si>
-  <si>
-    <t>20122255</t>
-  </si>
-  <si>
-    <t>SDP MI BASO BLDK 77G</t>
-  </si>
-  <si>
-    <t>20135720</t>
-  </si>
-  <si>
-    <t>SDP MI KARI MRCON79G</t>
-  </si>
-  <si>
-    <t>20140678</t>
-  </si>
-  <si>
-    <t>SEDAAP SPC LAKSA CUP</t>
-  </si>
-  <si>
-    <t>10011850</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP MNT DNGN 160</t>
-  </si>
-  <si>
-    <t>PT,(E-5B)</t>
-  </si>
-  <si>
-    <t>10011851</t>
-  </si>
-  <si>
-    <t>H&amp;S A/D SMTH&amp;SLK 160</t>
-  </si>
-  <si>
-    <t>20049799</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP LMON FRS 160</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20118299</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP SPRM A.HF135</t>
-  </si>
-  <si>
-    <t>20039727</t>
-  </si>
-  <si>
-    <t>SHINZU'I MATSU 380ML</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20039728</t>
-  </si>
-  <si>
-    <t>SHINZU'I KIREI 380ML</t>
-  </si>
-  <si>
-    <t>20130653</t>
-  </si>
-  <si>
-    <t>SHINZU'I SKURA 380ML</t>
-  </si>
-  <si>
-    <t>20133798</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ EN.RS700</t>
-  </si>
-  <si>
-    <t>20135245</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ FRNCH700</t>
-  </si>
-  <si>
-    <t>20139729</t>
-  </si>
-  <si>
-    <t>SOKLN GR.TEA&amp;JSM 700</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
-  </si>
-  <si>
-    <t>PT</t>
+    <t>20113569</t>
+  </si>
+  <si>
+    <t>GRNR MC.WTR ROSE125</t>
+  </si>
+  <si>
+    <t>20127476</t>
+  </si>
+  <si>
+    <t>GRNR MC.WTR BHA 125</t>
+  </si>
+  <si>
+    <t>20137791</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ HJB 700</t>
+  </si>
+  <si>
+    <t>20067585</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ RED SB 700</t>
+  </si>
+  <si>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20046548</t>
+  </si>
+  <si>
+    <t>SOKLIN SOFT CAIR 700</t>
+  </si>
+  <si>
+    <t>20054747</t>
+  </si>
+  <si>
+    <t>SO KLIN VL/BLSOM 700</t>
   </si>
 </sst>
 </file>
@@ -622,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -686,18 +677,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -706,18 +697,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -726,18 +717,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -746,18 +737,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -766,258 +757,258 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1026,18 +1017,18 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1046,18 +1037,18 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1066,170 +1057,190 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
   <si>
     <t/>
   </si>
   <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
+    <t>20036197</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 1 LT</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,199 +28,157 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20036198</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO PET1L</t>
+  </si>
+  <si>
+    <t>20036199</t>
+  </si>
+  <si>
+    <t>FANTA STRAWBERRY 1 L</t>
+  </si>
+  <si>
+    <t>20036200</t>
+  </si>
+  <si>
+    <t>SPRITE SOFT DRINK 1L</t>
+  </si>
+  <si>
+    <t>20133979</t>
+  </si>
+  <si>
+    <t>SPRITE ZERO LIME 1LT</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
-    <t>10025006</t>
-  </si>
-  <si>
-    <t>NESTLE KOKO.COMBO 30</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20046903</t>
-  </si>
-  <si>
-    <t>NESTLE HONY STAR 30G</t>
-  </si>
-  <si>
-    <t>20111959</t>
-  </si>
-  <si>
-    <t>KOKO KRNCH DB.CHO 30</t>
-  </si>
-  <si>
-    <t>20032723</t>
-  </si>
-  <si>
-    <t>MILO CEREAL COKLT 30</t>
+    <t>20140013</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHOC CRSPY 30G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10004490</t>
-  </si>
-  <si>
-    <t>HELLO PANDA STRW 42G</t>
+    <t>20140016</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHO PEANUT 37G</t>
+  </si>
+  <si>
+    <t>20088712</t>
+  </si>
+  <si>
+    <t>SASA SANT.KLP CAIR65</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10038704</t>
-  </si>
-  <si>
-    <t>MEIJI H/PANDA CHOC42</t>
-  </si>
-  <si>
-    <t>20134559</t>
-  </si>
-  <si>
-    <t>HLO PANDA DB.CHO 42G</t>
-  </si>
-  <si>
-    <t>20107748</t>
-  </si>
-  <si>
-    <t>MILKU SUSU CKLT 200</t>
-  </si>
-  <si>
-    <t>20107749</t>
-  </si>
-  <si>
-    <t>MILKU SUSU STRO 200</t>
-  </si>
-  <si>
-    <t>20134047</t>
-  </si>
-  <si>
-    <t>MILKU SUSU ORGNAL200</t>
-  </si>
-  <si>
-    <t>20141102</t>
-  </si>
-  <si>
-    <t>MILKU UHT MARIE 200</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>20034685</t>
-  </si>
-  <si>
-    <t>OISHI PILLOW CHO 100</t>
-  </si>
-  <si>
-    <t>20034686</t>
-  </si>
-  <si>
-    <t>OISHI PILLOW UBI 100</t>
-  </si>
-  <si>
-    <t>20045784</t>
-  </si>
-  <si>
-    <t>OISHI SPNG/C CHO 100</t>
-  </si>
-  <si>
-    <t>20047335</t>
-  </si>
-  <si>
-    <t>OISHI SPNG STRW 100G</t>
-  </si>
-  <si>
-    <t>20136289</t>
-  </si>
-  <si>
-    <t>OISHI SPONGE UBI 100</t>
-  </si>
-  <si>
-    <t>20141746</t>
-  </si>
-  <si>
-    <t>OISHI PLLOW STRW 100</t>
-  </si>
-  <si>
-    <t>20073377</t>
-  </si>
-  <si>
-    <t>GRNIER MC.CLN PNK125</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20113219</t>
-  </si>
-  <si>
-    <t>GNR MCL/WTR VITC 125</t>
-  </si>
-  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20113569</t>
-  </si>
-  <si>
-    <t>GRNR MC.WTR ROSE125</t>
-  </si>
-  <si>
-    <t>20127476</t>
-  </si>
-  <si>
-    <t>GRNR MC.WTR BHA 125</t>
-  </si>
-  <si>
-    <t>20137791</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ HJB 700</t>
-  </si>
-  <si>
-    <t>20067585</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ RED SB 700</t>
-  </si>
-  <si>
-    <t>20131625</t>
-  </si>
-  <si>
-    <t>LARISST FCL.TIS 250S</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20046548</t>
-  </si>
-  <si>
-    <t>SOKLIN SOFT CAIR 700</t>
-  </si>
-  <si>
-    <t>20054747</t>
-  </si>
-  <si>
-    <t>SO KLIN VL/BLSOM 700</t>
+    <t>10008819</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 700G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>20108264</t>
+  </si>
+  <si>
+    <t>SARI ROTI TAWAR JMBO</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20084152</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW MLD C800</t>
+  </si>
+  <si>
+    <t>20087202</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 800</t>
+  </si>
+  <si>
+    <t>20140968</t>
+  </si>
+  <si>
+    <t>LFBUOY COOL FRS 800</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20071827</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 700</t>
+  </si>
+  <si>
+    <t>20085113</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 700</t>
+  </si>
+  <si>
+    <t>20105968</t>
+  </si>
+  <si>
+    <t>RNSO PWD JPN PC 700G</t>
   </si>
 </sst>
 </file>
@@ -613,14 +571,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -717,7 +675,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -725,11 +683,11 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -737,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -745,62 +703,62 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -817,430 +775,250 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="65">
   <si>
     <t/>
   </si>
   <si>
-    <t>20036197</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 1 LT</t>
+    <t>20092857</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 130</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,157 +28,184 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20036198</t>
-  </si>
-  <si>
-    <t>COCA COLA ZERO PET1L</t>
-  </si>
-  <si>
-    <t>20036199</t>
-  </si>
-  <si>
-    <t>FANTA STRAWBERRY 1 L</t>
-  </si>
-  <si>
-    <t>20036200</t>
-  </si>
-  <si>
-    <t>SPRITE SOFT DRINK 1L</t>
-  </si>
-  <si>
-    <t>20133979</t>
-  </si>
-  <si>
-    <t>SPRITE ZERO LIME 1LT</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140013</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHOC CRSPY 30G</t>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20140016</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHO PEANUT 37G</t>
-  </si>
-  <si>
-    <t>20088712</t>
-  </si>
-  <si>
-    <t>SASA SANT.KLP CAIR65</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
+  </si>
+  <si>
+    <t>20074112</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RICA 85G</t>
+  </si>
+  <si>
+    <t>20092858</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 145</t>
+  </si>
+  <si>
+    <t>20138106</t>
+  </si>
+  <si>
+    <t>TIC TIC STCK BWG 135</t>
+  </si>
+  <si>
+    <t>20104077</t>
+  </si>
+  <si>
+    <t>SEDAP KCP SPCL 725G</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
+  </si>
+  <si>
+    <t>20120180</t>
+  </si>
+  <si>
+    <t>SO SOFT RS&amp;WTRLY 700</t>
+  </si>
+  <si>
+    <t>20121364</t>
+  </si>
+  <si>
+    <t>SO SOFT SKR BLSM 700</t>
+  </si>
+  <si>
+    <t>20128720</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO BRS 700</t>
+  </si>
+  <si>
+    <t>20135246</t>
+  </si>
+  <si>
+    <t>SO SOFT SWT PEONY700</t>
+  </si>
+  <si>
+    <t>20140325</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO LILY 700</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20060386</t>
+  </si>
+  <si>
+    <t>GIV BW MLB&amp;CLG PC400</t>
+  </si>
+  <si>
+    <t>20073514</t>
+  </si>
+  <si>
+    <t>GIV BW FLW&amp;BER 400ML</t>
+  </si>
+  <si>
+    <t>20121017</t>
+  </si>
+  <si>
+    <t>GIV BW HJB SAF&amp;N 400</t>
+  </si>
+  <si>
+    <t>20138029</t>
+  </si>
+  <si>
+    <t>GIV BW SAKURA 400ML</t>
+  </si>
+  <si>
+    <t>20138875</t>
+  </si>
+  <si>
+    <t>GIV BW SF&amp;SM 400ML</t>
+  </si>
+  <si>
+    <t>20139653</t>
+  </si>
+  <si>
+    <t>LRST FAC.TIS 2X200S</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10008819</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 700G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>20108264</t>
-  </si>
-  <si>
-    <t>SARI ROTI TAWAR JMBO</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 800</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20084152</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW MLD C800</t>
-  </si>
-  <si>
-    <t>20087202</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 800</t>
-  </si>
-  <si>
-    <t>20140968</t>
-  </si>
-  <si>
-    <t>LFBUOY COOL FRS 800</t>
-  </si>
-  <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20071827</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 700</t>
-  </si>
-  <si>
-    <t>20085113</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 700</t>
-  </si>
-  <si>
-    <t>20105968</t>
-  </si>
-  <si>
-    <t>RNSO PWD JPN PC 700G</t>
+    <t>20091428</t>
+  </si>
+  <si>
+    <t>CLEAR/M SHP CL.SP160</t>
+  </si>
+  <si>
+    <t>20091440</t>
+  </si>
+  <si>
+    <t>CLEAR SHP MENTHOL160</t>
+  </si>
+  <si>
+    <t>20091441</t>
+  </si>
+  <si>
+    <t>CLEAR SHP KOMPLIT160</t>
+  </si>
+  <si>
+    <t>20132698</t>
+  </si>
+  <si>
+    <t>CLEAR SHP AK&amp;RNTK160</t>
   </si>
 </sst>
 </file>
@@ -571,14 +598,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -635,7 +662,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -643,19 +670,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -663,10 +690,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -675,18 +702,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -695,50 +722,50 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -752,13 +779,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -772,253 +799,373 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>49</v>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="62">
   <si>
     <t/>
   </si>
   <si>
-    <t>20092857</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 130</t>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -31,181 +31,172 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KARI AYAM 72G</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
-  </si>
-  <si>
-    <t>20074112</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RICA 85G</t>
-  </si>
-  <si>
-    <t>20092858</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 145</t>
-  </si>
-  <si>
-    <t>20138106</t>
-  </si>
-  <si>
-    <t>TIC TIC STCK BWG 135</t>
-  </si>
-  <si>
-    <t>20104077</t>
-  </si>
-  <si>
-    <t>SEDAP KCP SPCL 725G</t>
-  </si>
-  <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
-  </si>
-  <si>
-    <t>20120855</t>
-  </si>
-  <si>
-    <t>INDOMILK SWIS CHO535</t>
-  </si>
-  <si>
-    <t>20120180</t>
-  </si>
-  <si>
-    <t>SO SOFT RS&amp;WTRLY 700</t>
-  </si>
-  <si>
-    <t>20121364</t>
-  </si>
-  <si>
-    <t>SO SOFT SKR BLSM 700</t>
-  </si>
-  <si>
-    <t>20128720</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO BRS 700</t>
-  </si>
-  <si>
-    <t>20135246</t>
-  </si>
-  <si>
-    <t>SO SOFT SWT PEONY700</t>
-  </si>
-  <si>
-    <t>20140325</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO LILY 700</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20060386</t>
-  </si>
-  <si>
-    <t>GIV BW MLB&amp;CLG PC400</t>
-  </si>
-  <si>
-    <t>20073514</t>
-  </si>
-  <si>
-    <t>GIV BW FLW&amp;BER 400ML</t>
-  </si>
-  <si>
-    <t>20121017</t>
-  </si>
-  <si>
-    <t>GIV BW HJB SAF&amp;N 400</t>
-  </si>
-  <si>
-    <t>20138029</t>
-  </si>
-  <si>
-    <t>GIV BW SAKURA 400ML</t>
-  </si>
-  <si>
-    <t>20138875</t>
-  </si>
-  <si>
-    <t>GIV BW SF&amp;SM 400ML</t>
-  </si>
-  <si>
-    <t>20139653</t>
-  </si>
-  <si>
-    <t>LRST FAC.TIS 2X200S</t>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>10003485</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO ALMOND 52G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10036987</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO CASHEW 52G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20071780</t>
+  </si>
+  <si>
+    <t>POTABEE CHIP BBQ 65G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20071781</t>
+  </si>
+  <si>
+    <t>POTABEE CHIP SWD 65G</t>
+  </si>
+  <si>
+    <t>20093941</t>
+  </si>
+  <si>
+    <t>POTABEE AYM BKR 65G</t>
+  </si>
+  <si>
+    <t>20131098</t>
+  </si>
+  <si>
+    <t>POTABEE SPICY BBQ 65</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20084152</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW MLD C800</t>
+  </si>
+  <si>
+    <t>20087202</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 800</t>
+  </si>
+  <si>
+    <t>20140968</t>
+  </si>
+  <si>
+    <t>LFBUOY COOL FRS 800</t>
+  </si>
+  <si>
+    <t>20140223</t>
+  </si>
+  <si>
+    <t>LOREAL SHP F.R3X 200</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20140224</t>
+  </si>
+  <si>
+    <t>LOREAL SHP G.GLS 200</t>
+  </si>
+  <si>
+    <t>20140225</t>
+  </si>
+  <si>
+    <t>LOREAL CND G.GLS 175</t>
+  </si>
+  <si>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 660</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20091428</t>
-  </si>
-  <si>
-    <t>CLEAR/M SHP CL.SP160</t>
-  </si>
-  <si>
-    <t>20091440</t>
-  </si>
-  <si>
-    <t>CLEAR SHP MENTHOL160</t>
-  </si>
-  <si>
-    <t>20091441</t>
-  </si>
-  <si>
-    <t>CLEAR SHP KOMPLIT160</t>
-  </si>
-  <si>
-    <t>20132698</t>
-  </si>
-  <si>
-    <t>CLEAR SHP AK&amp;RNTK160</t>
+    <t>20086172</t>
+  </si>
+  <si>
+    <t>SNLIGHT MND.ORGE 600</t>
+  </si>
+  <si>
+    <t>20090067</t>
+  </si>
+  <si>
+    <t>SNLGHT MINT A.BAU600</t>
+  </si>
+  <si>
+    <t>20135144</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO NATURE600</t>
   </si>
 </sst>
 </file>
@@ -598,14 +589,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -665,35 +656,35 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -702,18 +693,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -722,18 +713,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -742,18 +733,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -765,15 +756,15 @@
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -785,35 +776,35 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -822,18 +813,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -842,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -850,322 +841,242 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
   <si>
     <t/>
   </si>
   <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
+    <t>20137992</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 1600ML</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -31,172 +31,178 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
+    <t>20137991</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 700ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>20138228</t>
+  </si>
+  <si>
+    <t>LAYS RUMPUT LAUT 64G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20138229</t>
+  </si>
+  <si>
+    <t>LAYS DGG SAPI BKR64G</t>
+  </si>
+  <si>
+    <t>20140882</t>
+  </si>
+  <si>
+    <t>LAYS WAVY SAPI 105G</t>
+  </si>
+  <si>
+    <t>20141504</t>
+  </si>
+  <si>
+    <t>LAYS RMPT LAUT PDS64</t>
+  </si>
+  <si>
+    <t>20046081</t>
+  </si>
+  <si>
+    <t>G/D 3IN1 MCCINO 10'S</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20060370</t>
+  </si>
+  <si>
+    <t>G/DAY CHOCOCINO 10'S</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20060371</t>
+  </si>
+  <si>
+    <t>G/DAY VNL.LATTE 10'S</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
+  </si>
+  <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>20139538</t>
+  </si>
+  <si>
+    <t>LAYS RMPT LAUT 105G</t>
+  </si>
+  <si>
+    <t>20118299</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP SPRM A.HF135</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10011851</t>
+  </si>
+  <si>
+    <t>H&amp;S A/D SMTH&amp;SLK 160</t>
+  </si>
+  <si>
+    <t>PT,(E-5B)</t>
+  </si>
+  <si>
+    <t>10011850</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP MNT DNGN 160</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10003485</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO ALMOND 52G</t>
+    <t>20049799</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP LMON FRS 160</t>
+  </si>
+  <si>
+    <t>10037208</t>
+  </si>
+  <si>
+    <t>CLOSE UP MT.FRSH 100</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
+    <t>10003569</t>
+  </si>
+  <si>
+    <t>CLOSE UP GRN E.FR160</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20071780</t>
-  </si>
-  <si>
-    <t>POTABEE CHIP BBQ 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20071781</t>
-  </si>
-  <si>
-    <t>POTABEE CHIP SWD 65G</t>
-  </si>
-  <si>
-    <t>20093941</t>
-  </si>
-  <si>
-    <t>POTABEE AYM BKR 65G</t>
-  </si>
-  <si>
-    <t>20131098</t>
-  </si>
-  <si>
-    <t>POTABEE SPICY BBQ 65</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
-  </si>
-  <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 800</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20084152</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW MLD C800</t>
-  </si>
-  <si>
-    <t>20087202</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 800</t>
-  </si>
-  <si>
-    <t>20140968</t>
-  </si>
-  <si>
-    <t>LFBUOY COOL FRS 800</t>
-  </si>
-  <si>
-    <t>20140223</t>
-  </si>
-  <si>
-    <t>LOREAL SHP F.R3X 200</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20140224</t>
-  </si>
-  <si>
-    <t>LOREAL SHP G.GLS 200</t>
-  </si>
-  <si>
-    <t>20140225</t>
-  </si>
-  <si>
-    <t>LOREAL CND G.GLS 175</t>
-  </si>
-  <si>
-    <t>20131625</t>
-  </si>
-  <si>
-    <t>LARISST FCL.TIS 250S</t>
-  </si>
-  <si>
     <t>PT,(E-4B)</t>
   </si>
   <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 660</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20086172</t>
-  </si>
-  <si>
-    <t>SNLIGHT MND.ORGE 600</t>
-  </si>
-  <si>
-    <t>20090067</t>
-  </si>
-  <si>
-    <t>SNLGHT MINT A.BAU600</t>
-  </si>
-  <si>
-    <t>20135144</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO NATURE600</t>
+    <t>20142133</t>
+  </si>
+  <si>
+    <t>VAPE MILK TEA 600ML</t>
+  </si>
+  <si>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>20136134</t>
+  </si>
+  <si>
+    <t>VAPE CANDY FLO 600</t>
+  </si>
+  <si>
+    <t>20020128</t>
+  </si>
+  <si>
+    <t>NICE FC/TISUE NP250S</t>
   </si>
 </sst>
 </file>
@@ -589,14 +595,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -656,15 +662,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -673,18 +679,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -693,18 +699,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -713,7 +719,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -721,10 +727,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -733,7 +739,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -741,10 +747,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -756,15 +762,15 @@
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -776,15 +782,15 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -796,15 +802,15 @@
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -813,18 +819,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -836,167 +842,167 @@
         <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1010,7 +1016,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>8</v>
@@ -1030,13 +1036,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1050,13 +1056,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1070,12 +1076,32 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>55</v>
       </c>
     </row>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="81">
   <si>
     <t/>
   </si>
   <si>
-    <t>20137992</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 1600ML</t>
+    <t>10000426</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL1500</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,181 +28,232 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KURMA SUSU KR189</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20137991</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 700ML</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20138228</t>
-  </si>
-  <si>
-    <t>LAYS RUMPUT LAUT 64G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20138229</t>
-  </si>
-  <si>
-    <t>LAYS DGG SAPI BKR64G</t>
-  </si>
-  <si>
-    <t>20140882</t>
-  </si>
-  <si>
-    <t>LAYS WAVY SAPI 105G</t>
-  </si>
-  <si>
-    <t>20141504</t>
-  </si>
-  <si>
-    <t>LAYS RMPT LAUT PDS64</t>
-  </si>
-  <si>
-    <t>20046081</t>
-  </si>
-  <si>
-    <t>G/D 3IN1 MCCINO 10'S</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20060370</t>
-  </si>
-  <si>
-    <t>G/DAY CHOCOCINO 10'S</t>
+    <t>20076052</t>
+  </si>
+  <si>
+    <t>PUCUK TEH MLTI 1.3L</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>10036916</t>
+  </si>
+  <si>
+    <t>GLICO POCKY.STRAW 45</t>
+  </si>
+  <si>
+    <t>10000213</t>
+  </si>
+  <si>
+    <t>GLICO POCKY CHO 47GR</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20057865</t>
+  </si>
+  <si>
+    <t>GLCO POCKY DOU.CHO47</t>
+  </si>
+  <si>
+    <t>20062839</t>
+  </si>
+  <si>
+    <t>GLCO POCKY MTCHA 33G</t>
+  </si>
+  <si>
+    <t>20086168</t>
+  </si>
+  <si>
+    <t>GLCO POCKY COOK&amp;CR40</t>
+  </si>
+  <si>
+    <t>20138740</t>
+  </si>
+  <si>
+    <t>POCKY MILK CHOCO 39G</t>
+  </si>
+  <si>
+    <t>20138741</t>
+  </si>
+  <si>
+    <t>GLICO POCKY MILK 39G</t>
+  </si>
+  <si>
+    <t>20129837</t>
+  </si>
+  <si>
+    <t>LARIST SPR.GRD 750ML</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
+  </si>
+  <si>
+    <t>20128974</t>
+  </si>
+  <si>
+    <t>MONTISS FC TISUE200S</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20046056</t>
+  </si>
+  <si>
+    <t>MY BABY TLN PLUS 150</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20060371</t>
-  </si>
-  <si>
-    <t>G/DAY VNL.LATTE 10'S</t>
-  </si>
-  <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>20139538</t>
-  </si>
-  <si>
-    <t>LAYS RMPT LAUT 105G</t>
-  </si>
-  <si>
-    <t>20118299</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP SPRM A.HF135</t>
+    <t>20113916</t>
+  </si>
+  <si>
+    <t>MY BABY H&amp;B SWT 375</t>
+  </si>
+  <si>
+    <t>20125042</t>
+  </si>
+  <si>
+    <t>MYBABY TLN PLS LV150</t>
+  </si>
+  <si>
+    <t>20135627</t>
+  </si>
+  <si>
+    <t>MY BB H&amp;B WSH CLM375</t>
+  </si>
+  <si>
+    <t>20103167</t>
+  </si>
+  <si>
+    <t>MY BABY H&amp;B WSH 375</t>
+  </si>
+  <si>
+    <t>20067202</t>
+  </si>
+  <si>
+    <t>PONDS PW PR.CHR100G</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>10011851</t>
-  </si>
-  <si>
-    <t>H&amp;S A/D SMTH&amp;SLK 160</t>
-  </si>
-  <si>
-    <t>PT,(E-5B)</t>
-  </si>
-  <si>
-    <t>10011850</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP MNT DNGN 160</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20049799</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP LMON FRS 160</t>
-  </si>
-  <si>
-    <t>10037208</t>
-  </si>
-  <si>
-    <t>CLOSE UP MT.FRSH 100</t>
+    <t>20067210</t>
+  </si>
+  <si>
+    <t>PONDS PW NSRCNL 100G</t>
+  </si>
+  <si>
+    <t>20067449</t>
+  </si>
+  <si>
+    <t>GLW&amp;LOVELY DRM.GL100</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20110117</t>
+  </si>
+  <si>
+    <t>G&amp;L FC.FOAM VIT.C100</t>
+  </si>
+  <si>
+    <t>20042866</t>
+  </si>
+  <si>
+    <t>GRNIER ACNO FIGHT150</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10003569</t>
-  </si>
-  <si>
-    <t>CLOSE UP GRN E.FR160</t>
+    <t>20034274</t>
+  </si>
+  <si>
+    <t>GRNR MEN ICY SCRB100</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20142133</t>
-  </si>
-  <si>
-    <t>VAPE MILK TEA 600ML</t>
-  </si>
-  <si>
-    <t>10006651</t>
-  </si>
-  <si>
-    <t>VAPE FMK ORANGE 600</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20124850</t>
-  </si>
-  <si>
-    <t>VAPE SPRY SWET PD600</t>
-  </si>
-  <si>
-    <t>20136130</t>
-  </si>
-  <si>
-    <t>VAPE FLO.BUBBLE 600</t>
-  </si>
-  <si>
-    <t>20136134</t>
-  </si>
-  <si>
-    <t>VAPE CANDY FLO 600</t>
-  </si>
-  <si>
-    <t>20020128</t>
-  </si>
-  <si>
-    <t>NICE FC/TISUE NP250S</t>
+    <t>20052043</t>
+  </si>
+  <si>
+    <t>GRNIER MEN WSABI 100</t>
+  </si>
+  <si>
+    <t>20053651</t>
+  </si>
+  <si>
+    <t>GRN MEN TB DUO.FM150</t>
+  </si>
+  <si>
+    <t>20073377</t>
+  </si>
+  <si>
+    <t>GRNIER MC.CLN PNK125</t>
+  </si>
+  <si>
+    <t>20113219</t>
+  </si>
+  <si>
+    <t>GNR MCL/WTR VITC 125</t>
+  </si>
+  <si>
+    <t>20113569</t>
+  </si>
+  <si>
+    <t>GRNR MC.WTR ROSE125</t>
+  </si>
+  <si>
+    <t>20127476</t>
+  </si>
+  <si>
+    <t>GRNR MC.WTR BHA 125</t>
   </si>
 </sst>
 </file>
@@ -595,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -682,75 +733,75 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -759,10 +810,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -779,10 +830,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -799,10 +850,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -819,19 +870,19 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
@@ -839,19 +890,19 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
@@ -859,38 +910,38 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -899,18 +950,18 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -919,18 +970,18 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -939,64 +990,64 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>4</v>
@@ -1007,36 +1058,36 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>8</v>
@@ -1047,62 +1098,242 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>55</v>
+      <c r="B27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="86">
   <si>
     <t/>
   </si>
   <si>
-    <t>10000426</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL1500</t>
+    <t>20085988</t>
+  </si>
+  <si>
+    <t>LE MINERALE 1500ML</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,232 +28,247 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20055204</t>
+  </si>
+  <si>
+    <t>TARO POTATO BBQ 62G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20055205</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 62G</t>
+  </si>
+  <si>
+    <t>20081238</t>
+  </si>
+  <si>
+    <t>TARO NET TRYK BBQ 62</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20076052</t>
-  </si>
-  <si>
-    <t>PUCUK TEH MLTI 1.3L</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>10036916</t>
-  </si>
-  <si>
-    <t>GLICO POCKY.STRAW 45</t>
-  </si>
-  <si>
-    <t>10000213</t>
-  </si>
-  <si>
-    <t>GLICO POCKY CHO 47GR</t>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>20093135</t>
+  </si>
+  <si>
+    <t>BENG-BENG SHR IT 10S</t>
+  </si>
+  <si>
+    <t>20044008</t>
+  </si>
+  <si>
+    <t>BENG-BENG MAXX 32G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20057865</t>
-  </si>
-  <si>
-    <t>GLCO POCKY DOU.CHO47</t>
-  </si>
-  <si>
-    <t>20062839</t>
-  </si>
-  <si>
-    <t>GLCO POCKY MTCHA 33G</t>
-  </si>
-  <si>
-    <t>20086168</t>
-  </si>
-  <si>
-    <t>GLCO POCKY COOK&amp;CR40</t>
-  </si>
-  <si>
-    <t>20138740</t>
-  </si>
-  <si>
-    <t>POCKY MILK CHOCO 39G</t>
-  </si>
-  <si>
-    <t>20138741</t>
-  </si>
-  <si>
-    <t>GLICO POCKY MILK 39G</t>
-  </si>
-  <si>
-    <t>20129837</t>
-  </si>
-  <si>
-    <t>LARIST SPR.GRD 750ML</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
-  </si>
-  <si>
-    <t>20128974</t>
-  </si>
-  <si>
-    <t>MONTISS FC TISUE200S</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20046056</t>
-  </si>
-  <si>
-    <t>MY BABY TLN PLUS 150</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20113916</t>
-  </si>
-  <si>
-    <t>MY BABY H&amp;B SWT 375</t>
-  </si>
-  <si>
-    <t>20125042</t>
-  </si>
-  <si>
-    <t>MYBABY TLN PLS LV150</t>
-  </si>
-  <si>
-    <t>20135627</t>
-  </si>
-  <si>
-    <t>MY BB H&amp;B WSH CLM375</t>
-  </si>
-  <si>
-    <t>20103167</t>
-  </si>
-  <si>
-    <t>MY BABY H&amp;B WSH 375</t>
-  </si>
-  <si>
-    <t>20067202</t>
-  </si>
-  <si>
-    <t>PONDS PW PR.CHR100G</t>
+    <t>20130709</t>
+  </si>
+  <si>
+    <t>LUX BW MGC ORCHD 825</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20067210</t>
-  </si>
-  <si>
-    <t>PONDS PW NSRCNL 100G</t>
-  </si>
-  <si>
-    <t>20067449</t>
-  </si>
-  <si>
-    <t>GLW&amp;LOVELY DRM.GL100</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20110117</t>
-  </si>
-  <si>
-    <t>G&amp;L FC.FOAM VIT.C100</t>
-  </si>
-  <si>
-    <t>20042866</t>
-  </si>
-  <si>
-    <t>GRNIER ACNO FIGHT150</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20034274</t>
-  </si>
-  <si>
-    <t>GRNR MEN ICY SCRB100</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20052043</t>
-  </si>
-  <si>
-    <t>GRNIER MEN WSABI 100</t>
-  </si>
-  <si>
-    <t>20053651</t>
-  </si>
-  <si>
-    <t>GRN MEN TB DUO.FM150</t>
-  </si>
-  <si>
-    <t>20073377</t>
-  </si>
-  <si>
-    <t>GRNIER MC.CLN PNK125</t>
-  </si>
-  <si>
-    <t>20113219</t>
-  </si>
-  <si>
-    <t>GNR MCL/WTR VITC 125</t>
-  </si>
-  <si>
-    <t>20113569</t>
-  </si>
-  <si>
-    <t>GRNR MC.WTR ROSE125</t>
-  </si>
-  <si>
-    <t>20127476</t>
-  </si>
-  <si>
-    <t>GRNR MC.WTR BHA 125</t>
+    <t>20130710</t>
+  </si>
+  <si>
+    <t>LUX BW SKURA BLM 825</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
+  </si>
+  <si>
+    <t>20084152</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW MLD C800</t>
+  </si>
+  <si>
+    <t>20087202</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 800</t>
+  </si>
+  <si>
+    <t>20140968</t>
+  </si>
+  <si>
+    <t>LFBUOY COOL FRS 800</t>
+  </si>
+  <si>
+    <t>20067359</t>
+  </si>
+  <si>
+    <t>SUNSLK SHP HJB RE160</t>
+  </si>
+  <si>
+    <t>20138898</t>
+  </si>
+  <si>
+    <t>SNSLK SHP S.SMTH 160</t>
+  </si>
+  <si>
+    <t>20138899</t>
+  </si>
+  <si>
+    <t>SNSLK SHP G.BLCK 160</t>
+  </si>
+  <si>
+    <t>20138900</t>
+  </si>
+  <si>
+    <t>SNSLK SHP AD</t>
+  </si>
+  <si>
+    <t>20138902</t>
+  </si>
+  <si>
+    <t>SNSLK SHP S.SMTH 320</t>
+  </si>
+  <si>
+    <t>20138903</t>
+  </si>
+  <si>
+    <t>SNSLK SHP G.BLCK 320</t>
+  </si>
+  <si>
+    <t>20040702</t>
+  </si>
+  <si>
+    <t>PEPSODENT FRSH/CL190</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
+  </si>
+  <si>
+    <t>10004068</t>
+  </si>
+  <si>
+    <t>MAMA LIME POUCH 690</t>
+  </si>
+  <si>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 690</t>
+  </si>
+  <si>
+    <t>20052031</t>
+  </si>
+  <si>
+    <t>MAMA LIME GRN TEA690</t>
+  </si>
+  <si>
+    <t>20099424</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 690</t>
+  </si>
+  <si>
+    <t>20134303</t>
+  </si>
+  <si>
+    <t>MAMA/L REF YUZU 690</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>10004067</t>
+  </si>
+  <si>
+    <t>MAMA/L PCH LEMON 690</t>
+  </si>
+  <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
+  </si>
+  <si>
+    <t>20115958</t>
+  </si>
+  <si>
+    <t>GENTLE GEN PRS.G 700</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
+  </si>
+  <si>
+    <t>20133333</t>
+  </si>
+  <si>
+    <t>GENTLE GEN A/KRGT700</t>
+  </si>
+  <si>
+    <t>20141371</t>
+  </si>
+  <si>
+    <t>GNTLE GEN CMLLIA 700</t>
+  </si>
+  <si>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LILAC 700</t>
   </si>
 </sst>
 </file>
@@ -646,14 +661,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -713,15 +728,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -730,50 +745,50 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -787,13 +802,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -810,10 +825,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -830,10 +845,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -850,10 +865,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -870,10 +885,10 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -890,110 +905,110 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1007,290 +1022,290 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1298,19 +1313,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1318,21 +1333,101 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" s="1" t="s">
+      <c r="B36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="75">
   <si>
     <t/>
   </si>
   <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500ML</t>
+    <t>10003485</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO ALMND 52 G</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -31,244 +31,211 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20055204</t>
-  </si>
-  <si>
-    <t>TARO POTATO BBQ 62G</t>
+    <t>10036987</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO CASHW 52 G</t>
+  </si>
+  <si>
+    <t>20025741</t>
+  </si>
+  <si>
+    <t>ROMA SR GANDUM 149 G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>20045132</t>
+  </si>
+  <si>
+    <t>ROMA GNDM SAND 108 G</t>
+  </si>
+  <si>
+    <t>20052934</t>
+  </si>
+  <si>
+    <t>ROMA GNDM PNUT 108 G</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NSCAFE LATTE 220 ML</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20055205</t>
-  </si>
-  <si>
-    <t>TARO SEAWEED 62G</t>
-  </si>
-  <si>
-    <t>20081238</t>
-  </si>
-  <si>
-    <t>TARO NET TRYK BBQ 62</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
+    <t>20114494</t>
+  </si>
+  <si>
+    <t>NSCAFE C MCTO 220 ML</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NSCAFE CPCCN 220 ML</t>
+  </si>
+  <si>
+    <t>20138057</t>
+  </si>
+  <si>
+    <t>NSCAFE G AREN 220 ML</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE I BLCK 220 ML</t>
+  </si>
+  <si>
+    <t>20093909</t>
+  </si>
+  <si>
+    <t>REBO KUACI MLK 120 G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CLGEN 189</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>20093135</t>
-  </si>
-  <si>
-    <t>BENG-BENG SHR IT 10S</t>
-  </si>
-  <si>
-    <t>20044008</t>
-  </si>
-  <si>
-    <t>BENG-BENG MAXX 32G</t>
+    <t>20068536</t>
+  </si>
+  <si>
+    <t>REBO KUACI G.T 120 G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20130709</t>
-  </si>
-  <si>
-    <t>LUX BW MGC ORCHD 825</t>
+    <t>20098334</t>
+  </si>
+  <si>
+    <t>REBO KUACI CRM 120 G</t>
+  </si>
+  <si>
+    <t>20098348</t>
+  </si>
+  <si>
+    <t>REBO KUACI ORI 120 G</t>
+  </si>
+  <si>
+    <t>20130147</t>
+  </si>
+  <si>
+    <t>REBO KUACI CNT 120 G</t>
+  </si>
+  <si>
+    <t>10000425</t>
+  </si>
+  <si>
+    <t>C/LANG MIKAPU 60 ML</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>10002941</t>
+  </si>
+  <si>
+    <t>C/LANG MIKAPU 120 ML</t>
+  </si>
+  <si>
+    <t>10003569</t>
+  </si>
+  <si>
+    <t>CLOSE UP GRN F 160 G</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10037208</t>
+  </si>
+  <si>
+    <t>CLOSE UP MT.FH 100 G</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20130710</t>
-  </si>
-  <si>
-    <t>LUX BW SKURA BLM 825</t>
-  </si>
-  <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 800</t>
-  </si>
-  <si>
-    <t>20084152</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW MLD C800</t>
-  </si>
-  <si>
-    <t>20087202</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 800</t>
-  </si>
-  <si>
-    <t>20140968</t>
-  </si>
-  <si>
-    <t>LFBUOY COOL FRS 800</t>
-  </si>
-  <si>
-    <t>20067359</t>
-  </si>
-  <si>
-    <t>SUNSLK SHP HJB RE160</t>
-  </si>
-  <si>
-    <t>20138898</t>
-  </si>
-  <si>
-    <t>SNSLK SHP S.SMTH 160</t>
-  </si>
-  <si>
-    <t>20138899</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 160</t>
-  </si>
-  <si>
-    <t>20138900</t>
-  </si>
-  <si>
-    <t>SNSLK SHP AD</t>
-  </si>
-  <si>
-    <t>20138902</t>
-  </si>
-  <si>
-    <t>SNSLK SHP S.SMTH 320</t>
-  </si>
-  <si>
-    <t>20138903</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 320</t>
-  </si>
-  <si>
-    <t>20040702</t>
-  </si>
-  <si>
-    <t>PEPSODENT FRSH/CL190</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
-  </si>
-  <si>
-    <t>10004068</t>
-  </si>
-  <si>
-    <t>MAMA LIME POUCH 690</t>
-  </si>
-  <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 690</t>
-  </si>
-  <si>
-    <t>20052031</t>
-  </si>
-  <si>
-    <t>MAMA LIME GRN TEA690</t>
-  </si>
-  <si>
-    <t>20099424</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 690</t>
-  </si>
-  <si>
-    <t>20134303</t>
-  </si>
-  <si>
-    <t>MAMA/L REF YUZU 690</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>MAMA/L PCH LEMON 690</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
-  </si>
-  <si>
-    <t>20115958</t>
-  </si>
-  <si>
-    <t>GENTLE GEN PRS.G 700</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>20133333</t>
-  </si>
-  <si>
-    <t>GENTLE GEN A/KRGT700</t>
-  </si>
-  <si>
-    <t>20141371</t>
-  </si>
-  <si>
-    <t>GNTLE GEN CMLLIA 700</t>
-  </si>
-  <si>
-    <t>20141372</t>
-  </si>
-  <si>
-    <t>GENTLE GEN LILAC 700</t>
+    <t>20039727</t>
+  </si>
+  <si>
+    <t>SHINZU'I MATS 380 ML</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20039728</t>
+  </si>
+  <si>
+    <t>SHINZU'I KEI 380 ML</t>
+  </si>
+  <si>
+    <t>20130653</t>
+  </si>
+  <si>
+    <t>SHINZU'I SKRA 380 ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20093101</t>
+  </si>
+  <si>
+    <t>ZEN A.B SHISA 380 ML</t>
+  </si>
+  <si>
+    <t>20135211</t>
+  </si>
+  <si>
+    <t>ZEN A.B SHIJU 380 ML</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20140801</t>
+  </si>
+  <si>
+    <t>IDM TISU ROL 8'S</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON CTR FH 675 ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GN 675 ML</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BAYGON CH BLO 600 ML</t>
+  </si>
+  <si>
+    <t>20124346</t>
+  </si>
+  <si>
+    <t>BAYGON JP&amp;PCH 600 ML</t>
   </si>
 </sst>
 </file>
@@ -661,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -725,18 +692,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -745,19 +712,19 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,19 +732,19 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -785,7 +752,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -793,119 +760,119 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -913,142 +880,142 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1062,373 +1029,233 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="101">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003485</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO ALMND 52 G</t>
+    <t>20045784</t>
+  </si>
+  <si>
+    <t>OISHI SPNG/C CHO 100</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -31,211 +31,289 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHW 52 G</t>
-  </si>
-  <si>
-    <t>20025741</t>
-  </si>
-  <si>
-    <t>ROMA SR GANDUM 149 G</t>
+    <t>20047335</t>
+  </si>
+  <si>
+    <t>OISHI SPNG STRW 100G</t>
+  </si>
+  <si>
+    <t>20069696</t>
+  </si>
+  <si>
+    <t>OISHI POPCRN KRML100</t>
+  </si>
+  <si>
+    <t>20069844</t>
+  </si>
+  <si>
+    <t>OISHI POPCRN COK 100</t>
+  </si>
+  <si>
+    <t>20125388</t>
+  </si>
+  <si>
+    <t>OISHI PCORN M/BLG100</t>
+  </si>
+  <si>
+    <t>20136289</t>
+  </si>
+  <si>
+    <t>OISHI SPONGE UBI 100</t>
+  </si>
+  <si>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20045132</t>
-  </si>
-  <si>
-    <t>ROMA GNDM SAND 108 G</t>
-  </si>
-  <si>
-    <t>20052934</t>
-  </si>
-  <si>
-    <t>ROMA GNDM PNUT 108 G</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NSCAFE LATTE 220 ML</t>
-  </si>
-  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20114494</t>
-  </si>
-  <si>
-    <t>NSCAFE C MCTO 220 ML</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NSCAFE CPCCN 220 ML</t>
-  </si>
-  <si>
-    <t>20138057</t>
-  </si>
-  <si>
-    <t>NSCAFE G AREN 220 ML</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE I BLCK 220 ML</t>
-  </si>
-  <si>
-    <t>20093909</t>
-  </si>
-  <si>
-    <t>REBO KUACI MLK 120 G</t>
+    <t>20015338</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CHSE 190</t>
+  </si>
+  <si>
+    <t>20095021</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CKLT 76G</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20068536</t>
-  </si>
-  <si>
-    <t>REBO KUACI G.T 120 G</t>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
+  </si>
+  <si>
+    <t>20018435</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 250ML</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20098334</t>
-  </si>
-  <si>
-    <t>REBO KUACI CRM 120 G</t>
-  </si>
-  <si>
-    <t>20098348</t>
-  </si>
-  <si>
-    <t>REBO KUACI ORI 120 G</t>
-  </si>
-  <si>
-    <t>20130147</t>
-  </si>
-  <si>
-    <t>REBO KUACI CNT 120 G</t>
-  </si>
-  <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C/LANG MIKAPU 60 ML</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>10002941</t>
-  </si>
-  <si>
-    <t>C/LANG MIKAPU 120 ML</t>
-  </si>
-  <si>
-    <t>10003569</t>
-  </si>
-  <si>
-    <t>CLOSE UP GRN F 160 G</t>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
+  </si>
+  <si>
+    <t>20104000</t>
+  </si>
+  <si>
+    <t>IDM KACANG ALMOND 65</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20128291</t>
+  </si>
+  <si>
+    <t>IDM KCG ALMD MADU 65</t>
+  </si>
+  <si>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
   </si>
   <si>
     <t>PT,(E-4B)</t>
   </si>
   <si>
-    <t>10037208</t>
-  </si>
-  <si>
-    <t>CLOSE UP MT.FH 100 G</t>
+    <t>20139653</t>
+  </si>
+  <si>
+    <t>LRST FAC.TIS 2X200S</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
+  </si>
+  <si>
+    <t>20115958</t>
+  </si>
+  <si>
+    <t>GENTLE GEN PRS.G 700</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
+  </si>
+  <si>
+    <t>20133333</t>
+  </si>
+  <si>
+    <t>GENTLE GEN A/KRGT700</t>
+  </si>
+  <si>
+    <t>20141371</t>
+  </si>
+  <si>
+    <t>GNTLE GEN CMLLIA 700</t>
+  </si>
+  <si>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LILAC 700</t>
+  </si>
+  <si>
+    <t>20138518</t>
+  </si>
+  <si>
+    <t>KILAU NIPIS 630ML</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>10011850</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP MNT DNGN 145</t>
+  </si>
+  <si>
+    <t>PT,(E-5B)</t>
+  </si>
+  <si>
+    <t>10011851</t>
+  </si>
+  <si>
+    <t>H&amp;S A/D SMTH&amp;SLK 145</t>
+  </si>
+  <si>
+    <t>20049799</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP LMON FRS 145</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20039727</t>
-  </si>
-  <si>
-    <t>SHINZU'I MATS 380 ML</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20039728</t>
-  </si>
-  <si>
-    <t>SHINZU'I KEI 380 ML</t>
-  </si>
-  <si>
-    <t>20130653</t>
-  </si>
-  <si>
-    <t>SHINZU'I SKRA 380 ML</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20093101</t>
-  </si>
-  <si>
-    <t>ZEN A.B SHISA 380 ML</t>
-  </si>
-  <si>
-    <t>20135211</t>
-  </si>
-  <si>
-    <t>ZEN A.B SHIJU 380 ML</t>
-  </si>
-  <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20140801</t>
-  </si>
-  <si>
-    <t>IDM TISU ROL 8'S</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON CTR FH 675 ML</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GN 675 ML</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BAYGON CH BLO 600 ML</t>
-  </si>
-  <si>
-    <t>20124346</t>
-  </si>
-  <si>
-    <t>BAYGON JP&amp;PCH 600 ML</t>
+    <t>20118299</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP SPRM A.HF135</t>
+  </si>
+  <si>
+    <t>20136586</t>
+  </si>
+  <si>
+    <t>H&amp;S 2IN1 MNTHL 145</t>
+  </si>
+  <si>
+    <t>20138023</t>
+  </si>
+  <si>
+    <t>H&amp;S 2IN1 SUTERA 145</t>
+  </si>
+  <si>
+    <t>10013360</t>
+  </si>
+  <si>
+    <t>BIORE BF RF P/MLD400</t>
+  </si>
+  <si>
+    <t>10013361</t>
+  </si>
+  <si>
+    <t>BIORE BF A.BACTR 400</t>
+  </si>
+  <si>
+    <t>20009499</t>
+  </si>
+  <si>
+    <t>BIORE BF WHT/S RF380</t>
+  </si>
+  <si>
+    <t>20009500</t>
+  </si>
+  <si>
+    <t>BIORE B.FOAM RELX400</t>
+  </si>
+  <si>
+    <t>20031215</t>
+  </si>
+  <si>
+    <t>BIORE BF LIVELY 400</t>
+  </si>
+  <si>
+    <t>20046176</t>
+  </si>
+  <si>
+    <t>BIORE BF ENRG.CL 400</t>
+  </si>
+  <si>
+    <t>20080927</t>
+  </si>
+  <si>
+    <t>BIORE BF CHRY SK 400</t>
+  </si>
+  <si>
+    <t>20120995</t>
+  </si>
+  <si>
+    <t>BIORE BF RELAX 725</t>
+  </si>
+  <si>
+    <t>20128894</t>
+  </si>
+  <si>
+    <t>BIORE BF BRGHT.LL400</t>
+  </si>
+  <si>
+    <t>20130824</t>
+  </si>
+  <si>
+    <t>BIORE BF FLOR SPA400</t>
+  </si>
+  <si>
+    <t>20142676</t>
+  </si>
+  <si>
+    <t>BIORE BF LEMONGR 725</t>
   </si>
 </sst>
 </file>
@@ -628,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -712,7 +790,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -720,11 +798,11 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -732,7 +810,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -740,11 +818,11 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,7 +830,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -760,42 +838,42 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -809,13 +887,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -829,50 +907,50 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -880,19 +958,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -909,30 +987,30 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -940,19 +1018,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -960,102 +1038,102 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1069,13 +1147,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1089,153 +1167,153 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1249,13 +1327,273 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>40</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="70">
   <si>
     <t/>
   </si>
   <si>
-    <t>20045784</t>
-  </si>
-  <si>
-    <t>OISHI SPNG/C CHO 100</t>
+    <t>20142495</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN 1L</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,292 +28,199 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20072194</t>
+  </si>
+  <si>
+    <t>MH MAITOS S.BLDO 120</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20072195</t>
+  </si>
+  <si>
+    <t>MH MAITOS JG.BBQ 120</t>
+  </si>
+  <si>
+    <t>20138147</t>
+  </si>
+  <si>
+    <t>CMORY EAT MLK HZL 80</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-7H)</t>
+  </si>
+  <si>
+    <t>20138150</t>
+  </si>
+  <si>
+    <t>CMORY EAT MLK CHO 80</t>
+  </si>
+  <si>
+    <t>20138151</t>
+  </si>
+  <si>
+    <t>CMORY EAT MLK MRIE80</t>
+  </si>
+  <si>
+    <t>20141051</t>
+  </si>
+  <si>
+    <t>CMRY EAT MILK MATCHA</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20047335</t>
-  </si>
-  <si>
-    <t>OISHI SPNG STRW 100G</t>
-  </si>
-  <si>
-    <t>20069696</t>
-  </si>
-  <si>
-    <t>OISHI POPCRN KRML100</t>
-  </si>
-  <si>
-    <t>20069844</t>
-  </si>
-  <si>
-    <t>OISHI POPCRN COK 100</t>
-  </si>
-  <si>
-    <t>20125388</t>
-  </si>
-  <si>
-    <t>OISHI PCORN M/BLG100</t>
-  </si>
-  <si>
-    <t>20136289</t>
-  </si>
-  <si>
-    <t>OISHI SPONGE UBI 100</t>
-  </si>
-  <si>
-    <t>20015337</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW COKL 190</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20015338</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CHSE 190</t>
-  </si>
-  <si>
-    <t>20095021</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CKLT 76G</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
-    <t>20018435</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 250ML</t>
+    <t>20085988</t>
+  </si>
+  <si>
+    <t>LE MINERALE 1500ML</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20076052</t>
+  </si>
+  <si>
+    <t>PUCUK TEH MLTI 1.3L</t>
+  </si>
+  <si>
+    <t>20104077</t>
+  </si>
+  <si>
+    <t>SEDAP KCP SPCL 725G</t>
+  </si>
+  <si>
+    <t>20052766</t>
+  </si>
+  <si>
+    <t>IDM KCNG METE MDU 80</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
-  </si>
-  <si>
-    <t>20120855</t>
-  </si>
-  <si>
-    <t>INDOMILK SWIS CHO535</t>
-  </si>
-  <si>
-    <t>20104000</t>
-  </si>
-  <si>
-    <t>IDM KACANG ALMOND 65</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20128291</t>
-  </si>
-  <si>
-    <t>IDM KCG ALMD MADU 65</t>
-  </si>
-  <si>
-    <t>20131625</t>
-  </si>
-  <si>
-    <t>LARISST FCL.TIS 250S</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20139653</t>
-  </si>
-  <si>
-    <t>LRST FAC.TIS 2X200S</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
-  </si>
-  <si>
-    <t>20115958</t>
-  </si>
-  <si>
-    <t>GENTLE GEN PRS.G 700</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>20133333</t>
-  </si>
-  <si>
-    <t>GENTLE GEN A/KRGT700</t>
-  </si>
-  <si>
-    <t>20141371</t>
-  </si>
-  <si>
-    <t>GNTLE GEN CMLLIA 700</t>
-  </si>
-  <si>
-    <t>20141372</t>
-  </si>
-  <si>
-    <t>GENTLE GEN LILAC 700</t>
-  </si>
-  <si>
-    <t>20138518</t>
-  </si>
-  <si>
-    <t>KILAU NIPIS 630ML</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>10011850</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP MNT DNGN 145</t>
-  </si>
-  <si>
-    <t>PT,(E-5B)</t>
-  </si>
-  <si>
-    <t>10011851</t>
-  </si>
-  <si>
-    <t>H&amp;S A/D SMTH&amp;SLK 145</t>
-  </si>
-  <si>
-    <t>20049799</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP LMON FRS 145</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20118299</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP SPRM A.HF135</t>
-  </si>
-  <si>
-    <t>20136586</t>
-  </si>
-  <si>
-    <t>H&amp;S 2IN1 MNTHL 145</t>
-  </si>
-  <si>
-    <t>20138023</t>
-  </si>
-  <si>
-    <t>H&amp;S 2IN1 SUTERA 145</t>
-  </si>
-  <si>
-    <t>10013360</t>
-  </si>
-  <si>
-    <t>BIORE BF RF P/MLD400</t>
-  </si>
-  <si>
-    <t>10013361</t>
-  </si>
-  <si>
-    <t>BIORE BF A.BACTR 400</t>
-  </si>
-  <si>
-    <t>20009499</t>
-  </si>
-  <si>
-    <t>BIORE BF WHT/S RF380</t>
-  </si>
-  <si>
-    <t>20009500</t>
-  </si>
-  <si>
-    <t>BIORE B.FOAM RELX400</t>
-  </si>
-  <si>
-    <t>20031215</t>
-  </si>
-  <si>
-    <t>BIORE BF LIVELY 400</t>
-  </si>
-  <si>
-    <t>20046176</t>
-  </si>
-  <si>
-    <t>BIORE BF ENRG.CL 400</t>
-  </si>
-  <si>
-    <t>20080927</t>
-  </si>
-  <si>
-    <t>BIORE BF CHRY SK 400</t>
-  </si>
-  <si>
-    <t>20120995</t>
-  </si>
-  <si>
-    <t>BIORE BF RELAX 725</t>
-  </si>
-  <si>
-    <t>20128894</t>
-  </si>
-  <si>
-    <t>BIORE BF BRGHT.LL400</t>
-  </si>
-  <si>
-    <t>20130824</t>
-  </si>
-  <si>
-    <t>BIORE BF FLOR SPA400</t>
-  </si>
-  <si>
-    <t>20142676</t>
-  </si>
-  <si>
-    <t>BIORE BF LEMONGR 725</t>
+    <t>20126521</t>
+  </si>
+  <si>
+    <t>IDM KCNG METE PDS 70</t>
+  </si>
+  <si>
+    <t>20134686</t>
+  </si>
+  <si>
+    <t>IDM KCG PISTACHIO 55</t>
+  </si>
+  <si>
+    <t>20129814</t>
+  </si>
+  <si>
+    <t>MLKITA CNDY BTES 24G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20140412</t>
+  </si>
+  <si>
+    <t>MILKITA MILKY BAR 15</t>
+  </si>
+  <si>
+    <t>20140906</t>
+  </si>
+  <si>
+    <t>MILKITA BAR CHOC 15G</t>
+  </si>
+  <si>
+    <t>20128974</t>
+  </si>
+  <si>
+    <t>MONTISS FC TISUE200S</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20127600</t>
+  </si>
+  <si>
+    <t>CPTADEN JB C.MINT225</t>
+  </si>
+  <si>
+    <t>20116823</t>
+  </si>
+  <si>
+    <t>CIPTADEN JB FRESH225</t>
+  </si>
+  <si>
+    <t>20008748</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID REF 45ML</t>
+  </si>
+  <si>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>20142133</t>
+  </si>
+  <si>
+    <t>VAPE MILK TEA 600ML</t>
+  </si>
+  <si>
+    <t>20084568</t>
+  </si>
+  <si>
+    <t>VAPE LIQ.SKR BLOSM45</t>
+  </si>
+  <si>
+    <t>20136134</t>
+  </si>
+  <si>
+    <t>VAPE CANDY FLO 600</t>
   </si>
 </sst>
 </file>
@@ -706,14 +613,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -770,18 +677,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -790,18 +697,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -810,18 +717,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -830,18 +737,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -850,18 +757,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -870,47 +777,47 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>24</v>
@@ -918,82 +825,82 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1007,10 +914,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1018,19 +925,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1038,22 +945,22 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1067,33 +974,33 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1107,33 +1014,33 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1147,13 +1054,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1167,13 +1074,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1187,13 +1094,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1207,13 +1114,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1227,13 +1134,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1247,352 +1154,72 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F44" s="1" t="s">
         <v>24</v>
       </c>
     </row>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="117">
   <si>
     <t/>
   </si>
   <si>
-    <t>20072317</t>
-  </si>
-  <si>
-    <t>CORNETTO OREO 110</t>
+    <t>20085988</t>
+  </si>
+  <si>
+    <t>LE MINERALE 1500ML</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,268 +28,340 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20025762</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PNG 65G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20122571</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PG 115G</t>
+  </si>
+  <si>
+    <t>20134572</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPRK 115</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20070253</t>
+  </si>
+  <si>
+    <t>FF COCONUT TPK 225ML</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20025753</t>
+  </si>
+  <si>
+    <t>F/F L/FAT COK TPK225</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
+  </si>
+  <si>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
+  </si>
+  <si>
+    <t>20088875</t>
+  </si>
+  <si>
+    <t>FF SWT.DLGHT TPK 225</t>
+  </si>
+  <si>
+    <t>20128754</t>
+  </si>
+  <si>
+    <t>FF SS.SEREAL CKL 225</t>
+  </si>
+  <si>
+    <t>20136768</t>
+  </si>
+  <si>
+    <t>F.FLAG UHT MATCH 225</t>
+  </si>
+  <si>
+    <t>20136769</t>
+  </si>
+  <si>
+    <t>F.FLAG UHT BERIS 225</t>
+  </si>
+  <si>
+    <t>20092331</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ JR.NP675</t>
+  </si>
+  <si>
+    <t>20107240</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ.SW&amp;JR675</t>
+  </si>
+  <si>
+    <t>20123812</t>
+  </si>
+  <si>
+    <t>EKONOMI LQ.SEREH 675</t>
+  </si>
+  <si>
+    <t>20135845</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ JR&amp;LMN650</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20136124</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ N&amp;JN 675G</t>
+  </si>
+  <si>
+    <t>20110001</t>
+  </si>
+  <si>
+    <t>WARDAH UV GRD GEL40</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500ML</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20129821</t>
-  </si>
-  <si>
-    <t>MAGNUM MATCHA.CRBL80</t>
-  </si>
-  <si>
-    <t>20134689</t>
-  </si>
-  <si>
-    <t>MAGNUM MNGO YOGHRT80</t>
-  </si>
-  <si>
-    <t>20138475</t>
-  </si>
-  <si>
-    <t>WALLS MGNUM STRW PAN</t>
-  </si>
-  <si>
-    <t>20139460</t>
-  </si>
-  <si>
-    <t>CORNETTO CHO HZL 108</t>
-  </si>
-  <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>20130152</t>
-  </si>
-  <si>
-    <t>LEMONILO BROWNIES 33</t>
-  </si>
-  <si>
-    <t>20132494</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS KJU33</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20137230</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS STR33</t>
-  </si>
-  <si>
-    <t>20142678</t>
-  </si>
-  <si>
-    <t>LMNILO LMN CHESSE 33</t>
-  </si>
-  <si>
-    <t>20040608</t>
-  </si>
-  <si>
-    <t>ZINC SHP HFT GNSG170</t>
-  </si>
-  <si>
-    <t>20040609</t>
-  </si>
-  <si>
-    <t>ZINC RE-FRSH COOL170</t>
-  </si>
-  <si>
-    <t>20099181</t>
-  </si>
-  <si>
-    <t>ZINC REFRSH COOL 340</t>
-  </si>
-  <si>
-    <t>20099182</t>
-  </si>
-  <si>
-    <t>ZINC HFT GINSENG 340</t>
-  </si>
-  <si>
-    <t>20109265</t>
-  </si>
-  <si>
-    <t>ZINC SHP LMN MINT170</t>
-  </si>
-  <si>
-    <t>20131028</t>
-  </si>
-  <si>
-    <t>ZINC SHP LMN MINT340</t>
-  </si>
-  <si>
-    <t>20136708</t>
-  </si>
-  <si>
-    <t>ZINC SHP COOL.BS 170</t>
-  </si>
-  <si>
-    <t>20040702</t>
-  </si>
-  <si>
-    <t>PEPSODENT FRSH/CL190</t>
+    <t>20131253</t>
+  </si>
+  <si>
+    <t>WARDAH UV AIRY SRM25</t>
+  </si>
+  <si>
+    <t>20134797</t>
+  </si>
+  <si>
+    <t>WRDH UV ACN/CL SUN35</t>
+  </si>
+  <si>
+    <t>20113402</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH E&amp;B 100</t>
+  </si>
+  <si>
+    <t>20113403</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH O&amp;C 100</t>
+  </si>
+  <si>
+    <t>20122091</t>
+  </si>
+  <si>
+    <t>KAHF FC.SCRB G/E 100</t>
+  </si>
+  <si>
+    <t>20135458</t>
+  </si>
+  <si>
+    <t>KAHF F/W ACNE&amp;POR100</t>
+  </si>
+  <si>
+    <t>20025002</t>
+  </si>
+  <si>
+    <t>GRNIER BC FW VT.C100</t>
+  </si>
+  <si>
+    <t>20040194</t>
+  </si>
+  <si>
+    <t>GRNR BC FWS.VT.C100</t>
+  </si>
+  <si>
+    <t>20052782</t>
+  </si>
+  <si>
+    <t>GRNIER SKR GLW HY100</t>
+  </si>
+  <si>
+    <t>20141978</t>
+  </si>
+  <si>
+    <t>GARNIER VITC LWPH100</t>
+  </si>
+  <si>
+    <t>20141979</t>
+  </si>
+  <si>
+    <t>GARNIER SKR GLOW 100</t>
+  </si>
+  <si>
+    <t>20073377</t>
+  </si>
+  <si>
+    <t>GRNIER MC.CLN PNK125</t>
+  </si>
+  <si>
+    <t>20113219</t>
+  </si>
+  <si>
+    <t>GNR MCL/WTR VITC 125</t>
+  </si>
+  <si>
+    <t>20113569</t>
+  </si>
+  <si>
+    <t>GRNR MC.WTR ROSE125</t>
+  </si>
+  <si>
+    <t>20127476</t>
+  </si>
+  <si>
+    <t>GRNR MC.WTR BHA 125</t>
+  </si>
+  <si>
+    <t>20139601</t>
+  </si>
+  <si>
+    <t>GRNIER MC.EXFO.W 125</t>
+  </si>
+  <si>
+    <t>20048847</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP900</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>20138867</t>
+  </si>
+  <si>
+    <t>RNSO JAP PEACH 700G</t>
+  </si>
+  <si>
+    <t>PT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20141203</t>
+  </si>
+  <si>
+    <t>RINSO RYL GOLD 700G</t>
+  </si>
+  <si>
+    <t>20141369</t>
+  </si>
+  <si>
+    <t>RINSO P.BRZE BTL 650</t>
+  </si>
+  <si>
+    <t>20141373</t>
+  </si>
+  <si>
+    <t>RINSO PW.CLN BTL 650</t>
+  </si>
+  <si>
+    <t>10037208</t>
+  </si>
+  <si>
+    <t>CLOSE UP MT.FRSH 100</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003569</t>
+  </si>
+  <si>
+    <t>CLOSE UP GRN E.FR160</t>
   </si>
   <si>
     <t>PT,(E-4B)</t>
   </si>
   <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20101378</t>
-  </si>
-  <si>
-    <t>KODOMO B.WIPE PNK 50</t>
-  </si>
-  <si>
-    <t>20115153</t>
-  </si>
-  <si>
-    <t>KODOMO B.WIPE A/B50S</t>
-  </si>
-  <si>
-    <t>20121413</t>
-  </si>
-  <si>
-    <t>KDMO B.WP ALOE 2X50S</t>
-  </si>
-  <si>
-    <t>20138144</t>
-  </si>
-  <si>
-    <t>KODOMO WPS H&amp;M 2X50S</t>
-  </si>
-  <si>
-    <t>20060392</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CARING 400</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20060393</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CLSC 400</t>
-  </si>
-  <si>
-    <t>20063269</t>
-  </si>
-  <si>
-    <t>NUVO CAIR NATURE 400</t>
-  </si>
-  <si>
-    <t>20114112</t>
-  </si>
-  <si>
-    <t>NUVO FRS.PRO LMN 400</t>
-  </si>
-  <si>
-    <t>20120877</t>
-  </si>
-  <si>
-    <t>NUVO CAIR MERAH 800</t>
-  </si>
-  <si>
-    <t>20120919</t>
-  </si>
-  <si>
-    <t>NUVO MILD PROTECT800</t>
-  </si>
-  <si>
-    <t>20138658</t>
-  </si>
-  <si>
-    <t>NUVO BW HYGIENIC 400</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 660</t>
-  </si>
-  <si>
-    <t>20086172</t>
-  </si>
-  <si>
-    <t>SNLIGHT MND.ORGE 600</t>
-  </si>
-  <si>
-    <t>20090067</t>
-  </si>
-  <si>
-    <t>SNLGHT MINT A.BAU600</t>
-  </si>
-  <si>
-    <t>20135144</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO NATURE600</t>
-  </si>
-  <si>
-    <t>20139947</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 675G</t>
-  </si>
-  <si>
-    <t>20139948</t>
-  </si>
-  <si>
-    <t>SNLGHT BERY&amp;LIME 675</t>
-  </si>
-  <si>
-    <t>20048847</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP900</t>
-  </si>
-  <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
+    <t>20037446</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ ROSE 700</t>
+  </si>
+  <si>
+    <t>20093521</t>
+  </si>
+  <si>
+    <t>RINSO+MOLTO ESC1440G</t>
+  </si>
+  <si>
+    <t>20139609</t>
+  </si>
+  <si>
+    <t>RNSO JPN PEAC 1440G</t>
+  </si>
+  <si>
+    <t>20140002</t>
+  </si>
+  <si>
+    <t>RINSO PWD PURE 1440G</t>
+  </si>
+  <si>
+    <t>20140003</t>
+  </si>
+  <si>
+    <t>RNSO PWD ROSE.F 1.44</t>
   </si>
 </sst>
 </file>
@@ -682,14 +754,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -746,18 +818,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -766,18 +838,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -786,590 +858,590 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1383,13 +1455,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1403,13 +1475,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1423,13 +1495,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1443,13 +1515,13 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1463,13 +1535,13 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1483,53 +1555,253 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>76</v>
+      <c r="F48" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,162 +11,168 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="54">
   <si>
     <t/>
   </si>
   <si>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA SRL 189 ML</t>
+  </si>
+  <si>
+    <t>PM1MKT</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MI GRG 5X91 G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20096590</t>
+  </si>
+  <si>
+    <t>SEDAAP MI STO 5x76 G</t>
+  </si>
+  <si>
+    <t>20113383</t>
+  </si>
+  <si>
+    <t>ROMA KLP FRS 6x23 G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20113989</t>
+  </si>
+  <si>
+    <t>ROMA KLP C CKL 186 G</t>
+  </si>
+  <si>
+    <t>20088730</t>
+  </si>
+  <si>
+    <t>KNZLR SNGL KEJU 60 G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-7H)</t>
+  </si>
+  <si>
+    <t>20141057</t>
+  </si>
+  <si>
+    <t>KNZLR S TOM YUM 60 G</t>
+  </si>
+  <si>
     <t>20069208</t>
   </si>
   <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>PM1MKT</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500ML</t>
-  </si>
-  <si>
-    <t>20138236</t>
-  </si>
-  <si>
-    <t>CHEETOS JGG BKR 120G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20138241</t>
-  </si>
-  <si>
-    <t>CHEETOS KEJU 120G</t>
-  </si>
-  <si>
-    <t>20063359</t>
-  </si>
-  <si>
-    <t>ROMA MLKST BLG/COK90</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20076052</t>
-  </si>
-  <si>
-    <t>PUCUK TEH MLTI 1.3L</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
-  </si>
-  <si>
-    <t>20142508</t>
-  </si>
-  <si>
-    <t>DARK WONDER  BDD2X40</t>
-  </si>
-  <si>
-    <t>20048847</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP900</t>
+    <t>LE MINERALE 600 ML</t>
+  </si>
+  <si>
+    <t>20031318</t>
+  </si>
+  <si>
+    <t>G/DAY CPCINO 10X25 G</t>
+  </si>
+  <si>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>K/A SPC MIX 10x23 G</t>
+  </si>
+  <si>
+    <t>20023845</t>
+  </si>
+  <si>
+    <t>PRINGLES CHESY 102 G</t>
+  </si>
+  <si>
+    <t>20023846</t>
+  </si>
+  <si>
+    <t>PRNGLES ORI 102 G</t>
+  </si>
+  <si>
+    <t>10011850</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP MNT D 160 ML</t>
+  </si>
+  <si>
+    <t>PT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20038763</t>
+  </si>
+  <si>
+    <t>PNTENE SHP AD 160 ML</t>
+  </si>
+  <si>
+    <t>10003569</t>
+  </si>
+  <si>
+    <t>CLOSE UP GRN F 160 G</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10037208</t>
+  </si>
+  <si>
+    <t>CLOSE UP MT.FH 100 G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10000425</t>
+  </si>
+  <si>
+    <t>C.LANG KYU PTH 60 ML</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20141441</t>
+  </si>
+  <si>
+    <t>C.LANG BAYI LVD 60 G</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLGHT LME PCH 660 G</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
-  </si>
-  <si>
-    <t>20138518</t>
-  </si>
-  <si>
-    <t>KILAU NIPIS 630ML</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20118537</t>
-  </si>
-  <si>
-    <t>PSODENT WHT 120+30G</t>
-  </si>
-  <si>
-    <t>20067210</t>
-  </si>
-  <si>
-    <t>PONDS PW NSRCNL 100G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20067449</t>
-  </si>
-  <si>
-    <t>GLW&amp;LOVELY DRM.GL100</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20091440</t>
-  </si>
-  <si>
-    <t>CLEAR SHP MENTHOL160</t>
-  </si>
-  <si>
-    <t>20138899</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 160</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SNLGHT J/NIPIS 675 G</t>
   </si>
 </sst>
 </file>
@@ -566,7 +572,7 @@
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -623,7 +629,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -631,10 +637,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -643,7 +649,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -663,7 +669,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -671,10 +677,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -683,7 +689,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -700,90 +706,90 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -791,22 +797,22 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -820,13 +826,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -840,10 +846,10 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>34</v>
@@ -860,33 +866,33 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -900,13 +906,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -920,10 +926,10 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>45</v>
@@ -940,53 +946,53 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/PM1MKT.xlsx
+++ b/E/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
   <si>
     <t/>
   </si>
   <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA SRL 189 ML</t>
+    <t>10000426</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL1500</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,151 +28,151 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MI GRG 5X91 G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20096590</t>
-  </si>
-  <si>
-    <t>SEDAAP MI STO 5x76 G</t>
-  </si>
-  <si>
-    <t>20113383</t>
-  </si>
-  <si>
-    <t>ROMA KLP FRS 6x23 G</t>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
+  </si>
+  <si>
+    <t>20052766</t>
+  </si>
+  <si>
+    <t>IDM KCNG METE MDU 80</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20113989</t>
-  </si>
-  <si>
-    <t>ROMA KLP C CKL 186 G</t>
-  </si>
-  <si>
-    <t>20088730</t>
-  </si>
-  <si>
-    <t>KNZLR SNGL KEJU 60 G</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20104000</t>
+  </si>
+  <si>
+    <t>IDM KACANG ALMOND 65</t>
+  </si>
+  <si>
+    <t>20135198</t>
+  </si>
+  <si>
+    <t>WONHAE YOG.GUM ORI48</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-7H)</t>
-  </si>
-  <si>
-    <t>20141057</t>
-  </si>
-  <si>
-    <t>KNZLR S TOM YUM 60 G</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600 ML</t>
-  </si>
-  <si>
-    <t>20031318</t>
-  </si>
-  <si>
-    <t>G/DAY CPCINO 10X25 G</t>
-  </si>
-  <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>K/A SPC MIX 10x23 G</t>
-  </si>
-  <si>
-    <t>20023845</t>
-  </si>
-  <si>
-    <t>PRINGLES CHESY 102 G</t>
-  </si>
-  <si>
-    <t>20023846</t>
-  </si>
-  <si>
-    <t>PRNGLES ORI 102 G</t>
-  </si>
-  <si>
-    <t>10011850</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP MNT D 160 ML</t>
-  </si>
-  <si>
-    <t>PT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20038763</t>
-  </si>
-  <si>
-    <t>PNTENE SHP AD 160 ML</t>
-  </si>
-  <si>
-    <t>10003569</t>
-  </si>
-  <si>
-    <t>CLOSE UP GRN F 160 G</t>
+    <t>20139890</t>
+  </si>
+  <si>
+    <t>WNHAE STRW CHEESCAKE</t>
+  </si>
+  <si>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MIN 600 ML</t>
+  </si>
+  <si>
+    <t>10008819</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 685G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20095226</t>
+  </si>
+  <si>
+    <t>TOP COFF CAPPCNO 6'S</t>
+  </si>
+  <si>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20107729</t>
+  </si>
+  <si>
+    <t>TOP COFF GL AREN 9'S</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20113403</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH O&amp;C 100</t>
+  </si>
+  <si>
+    <t>20130710</t>
+  </si>
+  <si>
+    <t>LUX BW SKURA BLM 825</t>
+  </si>
+  <si>
+    <t>20113402</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH E&amp;B 100</t>
+  </si>
+  <si>
+    <t>20046056</t>
+  </si>
+  <si>
+    <t>MY BABY TLN PLUS 150</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20027095</t>
+  </si>
+  <si>
+    <t>MY BABY TELON PLS 60</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
   </si>
   <si>
     <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10037208</t>
-  </si>
-  <si>
-    <t>CLOSE UP MT.FH 100 G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C.LANG KYU PTH 60 ML</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20141441</t>
-  </si>
-  <si>
-    <t>C.LANG BAYI LVD 60 G</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLGHT LME PCH 660 G</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SNLGHT J/NIPIS 675 G</t>
   </si>
 </sst>
 </file>
@@ -565,14 +565,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -632,15 +632,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -652,15 +652,15 @@
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -669,38 +669,38 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -709,38 +709,38 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -757,10 +757,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -772,15 +772,15 @@
         <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -789,18 +789,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -809,190 +809,170 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
